--- a/Consumables_Map.xlsx
+++ b/Consumables_Map.xlsx
@@ -40,8 +40,8 @@
     <definedName name="DDCounts">Config!$T$5:$AE$5</definedName>
     <definedName name="LogoSpot">Map!$AP$1</definedName>
     <definedName name="MapLegend">Map!$AL$6</definedName>
-    <definedName name="MapArea">Map!$A$1:$AU$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Map'!$A$1:$AU$30</definedName>
+    <definedName name="MapArea">Map!$A$1:$AU$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Map'!$A$1:$AU$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,13 +433,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -468,14 +468,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -783,7 +783,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblLocations" displayName="tblLocations" ref="A4:I420" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblLocations" displayName="tblLocations" ref="A4:I404" headerRowCount="1">
   <tableColumns count="9">
     <tableColumn id="1" name="LocationID"/>
     <tableColumn id="2" name="Aisle"/>
@@ -1141,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AU30"/>
+  <dimension ref="A1:AU29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.857142857142857" customWidth="1" min="1" max="1"/>
@@ -1301,31 +1301,51 @@
     </row>
     <row r="5" ht="15" customHeight="1"/>
     <row r="6" ht="15" customHeight="1">
-      <c r="R6" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>L3  Boxes</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
+      <c r="O6" s="8" t="n"/>
+      <c r="P6" s="8" t="n"/>
+      <c r="Q6" s="8" t="n"/>
+      <c r="R6" s="9" t="inlineStr">
         <is>
           <t>MAIN WALKWAY</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="U6" s="7" t="inlineStr">
         <is>
           <t>R4  Boxes</t>
         </is>
       </c>
-      <c r="V6" s="9" t="n"/>
-      <c r="W6" s="9" t="n"/>
-      <c r="X6" s="9" t="n"/>
-      <c r="Y6" s="9" t="n"/>
-      <c r="Z6" s="9" t="n"/>
-      <c r="AA6" s="9" t="n"/>
-      <c r="AB6" s="9" t="n"/>
-      <c r="AC6" s="9" t="n"/>
-      <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="9" t="n"/>
-      <c r="AF6" s="9" t="n"/>
-      <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="9" t="n"/>
-      <c r="AJ6" s="9" t="n"/>
+      <c r="V6" s="8" t="n"/>
+      <c r="W6" s="8" t="n"/>
+      <c r="X6" s="8" t="n"/>
+      <c r="Y6" s="8" t="n"/>
+      <c r="Z6" s="8" t="n"/>
+      <c r="AA6" s="8" t="n"/>
+      <c r="AB6" s="8" t="n"/>
+      <c r="AC6" s="8" t="n"/>
+      <c r="AD6" s="8" t="n"/>
+      <c r="AE6" s="8" t="n"/>
+      <c r="AF6" s="8" t="n"/>
+      <c r="AG6" s="8" t="n"/>
+      <c r="AH6" s="8" t="n"/>
+      <c r="AI6" s="8" t="n"/>
+      <c r="AJ6" s="8" t="n"/>
       <c r="AL6" s="10" t="inlineStr">
         <is>
           <t>ZONES</t>
@@ -1342,26 +1362,70 @@
       <c r="AU6" s="6" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>L3  Boxes</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="9" t="n"/>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="9" t="n"/>
-      <c r="N7" s="9" t="n"/>
-      <c r="O7" s="9" t="n"/>
-      <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="9" t="n"/>
+      <c r="B7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-16-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-15-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-14-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-13-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-12-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="G7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-11-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-10-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-09-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-08-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="K7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-07-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="L7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-06-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="M7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-05-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="N7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-04-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="O7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-03-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="P7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-02-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="Q7" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-01-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
       <c r="U7" s="11">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R4-01-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
@@ -1436,67 +1500,67 @@
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="B8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-16-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-16-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="C8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-15-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-15-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="D8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-14-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-14-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="E8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-13-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-13-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="F8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-12-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-12-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-11-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-11-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="H8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-10-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-10-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="I8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-09-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-09-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="J8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-08-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-08-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="K8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-07-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-07-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="L8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-06-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-06-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="M8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-05-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-05-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="N8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-04-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-04-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="O8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-03-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-03-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="P8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-02-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-02-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="Q8" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-01-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-01-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="U8" s="11">
@@ -1573,67 +1637,67 @@
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="B9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-16-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-16-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="C9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-15-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-15-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="D9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-14-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-14-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="E9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-13-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-13-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="F9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-12-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-12-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="G9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-11-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-11-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="H9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-10-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-10-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="I9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-09-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-09-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="J9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-08-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-08-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="K9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-07-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-07-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="L9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-06-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-06-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="M9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-05-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-05-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="N9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-04-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-04-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="O9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-03-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-03-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="P9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-02-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-02-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="Q9" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-01-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-01-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="U9" s="11">
@@ -1710,67 +1774,67 @@
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="B10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-16-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-16-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="C10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-15-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-15-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="D10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-14-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-14-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-13-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-13-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="F10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-12-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-12-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="G10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-11-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-11-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="H10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-10-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-10-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="I10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-09-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-09-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="J10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-08-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-08-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="K10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-07-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-07-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="L10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-06-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-06-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="M10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-05-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-05-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="N10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-04-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-04-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="O10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-03-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-03-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="P10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-02-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-02-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="Q10" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-01-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-01-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="U10" s="11">
@@ -1846,112 +1910,112 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-16-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="C11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-15-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="D11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-14-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="E11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-13-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-12-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="G11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-11-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-10-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-09-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-08-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="K11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-07-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="L11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-06-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="M11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-05-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="N11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-04-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="O11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-03-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="P11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-02-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="Q11" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L3-01-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>L2  Boxes</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+      <c r="M11" s="8" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="8" t="n"/>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="n"/>
+      <c r="U11" s="7" t="inlineStr">
         <is>
           <t>R3  Bags</t>
         </is>
       </c>
-      <c r="V11" s="9" t="n"/>
-      <c r="W11" s="9" t="n"/>
-      <c r="X11" s="9" t="n"/>
-      <c r="Y11" s="9" t="n"/>
-      <c r="Z11" s="9" t="n"/>
-      <c r="AA11" s="9" t="n"/>
-      <c r="AB11" s="9" t="n"/>
-      <c r="AC11" s="9" t="n"/>
-      <c r="AD11" s="9" t="n"/>
-      <c r="AE11" s="9" t="n"/>
-      <c r="AF11" s="9" t="n"/>
-      <c r="AG11" s="9" t="n"/>
-      <c r="AH11" s="9" t="n"/>
-      <c r="AI11" s="9" t="n"/>
-      <c r="AJ11" s="9" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="n"/>
+      <c r="Y11" s="8" t="n"/>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="n"/>
+      <c r="AD11" s="8" t="n"/>
+      <c r="AE11" s="8" t="n"/>
+      <c r="AF11" s="8" t="n"/>
+      <c r="AG11" s="8" t="n"/>
+      <c r="AH11" s="8" t="n"/>
+      <c r="AI11" s="8" t="n"/>
+      <c r="AJ11" s="8" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>L2  Boxes</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="9" t="n"/>
-      <c r="N12" s="9" t="n"/>
-      <c r="O12" s="9" t="n"/>
-      <c r="P12" s="9" t="n"/>
-      <c r="Q12" s="9" t="n"/>
+      <c r="B12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-16-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-15-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-14-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-13-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-12-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-11-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-10-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-09-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-08-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="K12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-07-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-06-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="M12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-05-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="N12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-04-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="O12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-03-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="P12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-02-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-01-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
       <c r="U12" s="21">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R3-01-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
@@ -2033,67 +2097,67 @@
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="B13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-16-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-16-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="C13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-15-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-15-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="D13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-14-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-14-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="E13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-13-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-13-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="F13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-12-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-12-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="G13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-11-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-11-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="H13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-10-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-10-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="I13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-09-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-09-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="J13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-08-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-08-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="K13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-07-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-07-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="L13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-06-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-06-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="M13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-05-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-05-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="N13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-04-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-04-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="O13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-03-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-03-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="P13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-02-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-02-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="Q13" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-01-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-01-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="U13" s="21">
@@ -2169,67 +2233,67 @@
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="B14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-16-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-16-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="C14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-15-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-15-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="D14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-14-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-14-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="E14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-13-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-13-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="F14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-12-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-12-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="G14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-11-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-11-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="H14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-10-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-10-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="I14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-09-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-09-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="J14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-08-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-08-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="K14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-07-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-07-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="L14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-06-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-06-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="M14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-05-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-05-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="N14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-04-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-04-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="O14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-03-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-03-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="P14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-02-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-02-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="Q14" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-01-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-01-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="U14" s="21">
@@ -2305,67 +2369,67 @@
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="B15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-16-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-16-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="C15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-15-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-15-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="D15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-14-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-14-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="E15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-13-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-13-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="F15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-12-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-12-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="G15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-11-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-11-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="H15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-10-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-10-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="I15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-09-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-09-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="J15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-08-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-08-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="K15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-07-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-07-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="L15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-06-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-06-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="M15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-05-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-05-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="N15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-04-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-04-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="O15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-03-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-03-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="P15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-02-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-02-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="Q15" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-01-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-01-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="U15" s="21">
@@ -2440,90 +2504,46 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-16-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="C16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-15-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-14-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-13-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-12-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-11-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-10-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-09-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-08-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="K16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-07-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="L16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-06-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-05-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="N16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-04-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="O16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-03-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="P16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-02-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="Q16" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L2-01-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>L1  Boxes</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="8" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="U16" s="7" t="inlineStr">
         <is>
           <t>R2  Films and Wrap</t>
         </is>
       </c>
-      <c r="V16" s="9" t="n"/>
-      <c r="W16" s="9" t="n"/>
-      <c r="X16" s="9" t="n"/>
-      <c r="Y16" s="9" t="n"/>
-      <c r="Z16" s="9" t="n"/>
-      <c r="AA16" s="9" t="n"/>
-      <c r="AB16" s="9" t="n"/>
-      <c r="AC16" s="9" t="n"/>
-      <c r="AD16" s="9" t="n"/>
-      <c r="AE16" s="9" t="n"/>
-      <c r="AF16" s="9" t="n"/>
-      <c r="AG16" s="9" t="n"/>
-      <c r="AH16" s="9" t="n"/>
-      <c r="AI16" s="9" t="n"/>
-      <c r="AJ16" s="9" t="n"/>
+      <c r="V16" s="8" t="n"/>
+      <c r="W16" s="8" t="n"/>
+      <c r="X16" s="8" t="n"/>
+      <c r="Y16" s="8" t="n"/>
+      <c r="Z16" s="8" t="n"/>
+      <c r="AA16" s="8" t="n"/>
+      <c r="AB16" s="8" t="n"/>
+      <c r="AC16" s="8" t="n"/>
+      <c r="AD16" s="8" t="n"/>
+      <c r="AE16" s="8" t="n"/>
+      <c r="AF16" s="8" t="n"/>
+      <c r="AG16" s="8" t="n"/>
+      <c r="AH16" s="8" t="n"/>
+      <c r="AI16" s="8" t="n"/>
+      <c r="AJ16" s="8" t="n"/>
       <c r="AL16" s="23" t="n"/>
       <c r="AO16" s="14" t="inlineStr">
         <is>
@@ -2532,26 +2552,70 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>L1  Boxes</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
-      <c r="L17" s="9" t="n"/>
-      <c r="M17" s="9" t="n"/>
-      <c r="N17" s="9" t="n"/>
-      <c r="O17" s="9" t="n"/>
-      <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="9" t="n"/>
+      <c r="B17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-16-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="C17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-15-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-14-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-13-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-12-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-11-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-10-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="I17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-09-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-08-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="K17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-07-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="L17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-06-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-05-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="N17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-04-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="O17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-03-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="P17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-02-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
+      <c r="Q17" s="11">
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-01-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <v/>
+      </c>
       <c r="U17" s="24">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R2-01-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
@@ -2625,67 +2689,67 @@
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="B18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-16-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-16-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="C18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-15-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-15-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="D18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-14-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-14-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="E18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-13-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-13-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="F18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-12-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-12-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="G18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-11-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-11-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="H18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-10-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-10-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="I18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-09-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-09-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="J18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-08-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-08-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="K18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-07-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-07-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="L18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-06-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-06-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="M18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-05-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-05-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="N18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-04-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-04-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="O18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-03-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-03-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="P18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-02-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-02-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="Q18" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-01-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-01-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="U18" s="24">
@@ -2761,67 +2825,67 @@
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="B19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-16-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-16-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="C19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-15-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-15-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="D19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-14-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-14-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="E19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-13-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-13-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="F19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-12-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-12-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="G19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-11-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-11-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="H19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-10-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-10-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="I19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-09-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-09-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="J19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-08-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-08-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="K19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-07-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-07-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="L19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-06-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-06-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="M19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-05-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-05-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="N19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-04-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-04-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="O19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-03-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-03-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="P19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-02-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-02-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="Q19" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-01-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-01-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="U19" s="24">
@@ -2897,67 +2961,67 @@
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-16-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-16-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="C20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-15-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-15-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="D20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-14-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-14-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="E20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-13-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-13-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="F20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-12-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-12-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="G20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-11-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-11-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="H20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-10-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-10-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="I20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-09-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-09-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="J20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-08-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-08-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="K20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-07-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-07-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="L20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-06-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-06-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="M20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-05-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-05-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="N20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-04-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-04-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="O20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-03-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-03-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="P20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-02-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-02-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="Q20" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-01-C",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
+        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-01-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
       <c r="U20" s="24">
@@ -3026,90 +3090,46 @@
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-16-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="C21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-15-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-14-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="E21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-13-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-12-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-11-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-10-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="I21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-09-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="J21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-08-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="K21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-07-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="L21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-06-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-05-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="N21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-04-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="O21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-03-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="P21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-02-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="Q21" s="11">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("L1-01-D",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>XL  Not ours</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="8" t="n"/>
+      <c r="K21" s="8" t="n"/>
+      <c r="L21" s="8" t="n"/>
+      <c r="M21" s="8" t="n"/>
+      <c r="N21" s="8" t="n"/>
+      <c r="O21" s="8" t="n"/>
+      <c r="P21" s="8" t="n"/>
+      <c r="Q21" s="8" t="n"/>
+      <c r="U21" s="7" t="inlineStr">
         <is>
           <t>R1  Labels and Packing</t>
         </is>
       </c>
-      <c r="V21" s="9" t="n"/>
-      <c r="W21" s="9" t="n"/>
-      <c r="X21" s="9" t="n"/>
-      <c r="Y21" s="9" t="n"/>
-      <c r="Z21" s="9" t="n"/>
-      <c r="AA21" s="9" t="n"/>
-      <c r="AB21" s="9" t="n"/>
-      <c r="AC21" s="9" t="n"/>
-      <c r="AD21" s="9" t="n"/>
-      <c r="AE21" s="9" t="n"/>
-      <c r="AF21" s="9" t="n"/>
-      <c r="AG21" s="9" t="n"/>
-      <c r="AH21" s="9" t="n"/>
-      <c r="AI21" s="9" t="n"/>
-      <c r="AJ21" s="9" t="n"/>
+      <c r="V21" s="8" t="n"/>
+      <c r="W21" s="8" t="n"/>
+      <c r="X21" s="8" t="n"/>
+      <c r="Y21" s="8" t="n"/>
+      <c r="Z21" s="8" t="n"/>
+      <c r="AA21" s="8" t="n"/>
+      <c r="AB21" s="8" t="n"/>
+      <c r="AC21" s="8" t="n"/>
+      <c r="AD21" s="8" t="n"/>
+      <c r="AE21" s="8" t="n"/>
+      <c r="AF21" s="8" t="n"/>
+      <c r="AG21" s="8" t="n"/>
+      <c r="AH21" s="8" t="n"/>
+      <c r="AI21" s="8" t="n"/>
+      <c r="AJ21" s="8" t="n"/>
       <c r="AL21" s="10" t="inlineStr">
         <is>
           <t>LIVE COUNTS</t>
@@ -3126,91 +3146,91 @@
       <c r="AU21" s="6" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>XL  Not ours</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
-      <c r="L22" s="9" t="n"/>
-      <c r="M22" s="9" t="n"/>
-      <c r="N22" s="9" t="n"/>
-      <c r="O22" s="9" t="n"/>
-      <c r="P22" s="9" t="n"/>
-      <c r="Q22" s="9" t="n"/>
-      <c r="U22" s="28">
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>NOT OURS</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="n"/>
+      <c r="I22" s="23" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="23" t="n"/>
+      <c r="L22" s="23" t="n"/>
+      <c r="M22" s="23" t="n"/>
+      <c r="N22" s="23" t="n"/>
+      <c r="O22" s="23" t="n"/>
+      <c r="P22" s="23" t="n"/>
+      <c r="Q22" s="23" t="n"/>
+      <c r="U22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-01-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="V22" s="28">
+      <c r="V22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-02-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="W22" s="28">
+      <c r="W22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-03-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="X22" s="28">
+      <c r="X22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-04-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="Y22" s="28">
+      <c r="Y22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-05-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="Z22" s="28">
+      <c r="Z22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-06-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="AA22" s="28">
+      <c r="AA22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-07-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="AB22" s="28">
+      <c r="AB22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-08-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="AC22" s="28">
+      <c r="AC22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-09-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="AD22" s="28">
+      <c r="AD22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-10-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="AE22" s="28">
+      <c r="AE22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-11-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="AF22" s="28">
+      <c r="AF22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-12-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="AG22" s="28">
+      <c r="AG22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-13-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="AH22" s="28">
+      <c r="AH22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-14-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="AI22" s="28">
+      <c r="AI22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-15-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="AJ22" s="28">
+      <c r="AJ22" s="29">
         <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-16-A",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
         <v/>
       </c>
-      <c r="AL22" s="29">
+      <c r="AL22" s="30">
         <f>ROWS(tblLocations[LocationID])</f>
         <v/>
       </c>
@@ -3221,11 +3241,7 @@
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="30" t="inlineStr">
-        <is>
-          <t>NOT OURS</t>
-        </is>
-      </c>
+      <c r="B23" s="23" t="n"/>
       <c r="C23" s="23" t="n"/>
       <c r="D23" s="23" t="n"/>
       <c r="E23" s="23" t="n"/>
@@ -3241,71 +3257,27 @@
       <c r="O23" s="23" t="n"/>
       <c r="P23" s="23" t="n"/>
       <c r="Q23" s="23" t="n"/>
-      <c r="U23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-01-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="V23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-02-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="W23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-03-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="X23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-04-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="Y23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-05-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="Z23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-06-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="AA23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-07-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="AB23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-08-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="AC23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-09-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="AD23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-10-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="AE23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-11-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="AF23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-12-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="AG23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-13-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="AH23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-14-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="AI23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-15-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="AJ23" s="28">
-        <f>IFERROR(LEFT(INDEX(tblLocations[ItemCode],MATCH("R1-16-B",tblLocations[LocationID],0))&amp;"",MapLabelChars),"")</f>
-        <v/>
-      </c>
-      <c r="AL23" s="29">
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>XR  Not ours</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="n"/>
+      <c r="W23" s="8" t="n"/>
+      <c r="X23" s="8" t="n"/>
+      <c r="Y23" s="8" t="n"/>
+      <c r="Z23" s="8" t="n"/>
+      <c r="AA23" s="8" t="n"/>
+      <c r="AB23" s="8" t="n"/>
+      <c r="AC23" s="8" t="n"/>
+      <c r="AD23" s="8" t="n"/>
+      <c r="AE23" s="8" t="n"/>
+      <c r="AF23" s="8" t="n"/>
+      <c r="AG23" s="8" t="n"/>
+      <c r="AH23" s="8" t="n"/>
+      <c r="AI23" s="8" t="n"/>
+      <c r="AJ23" s="8" t="n"/>
+      <c r="AL23" s="30">
         <f>COUNTIF(tblLocations[ItemCode],"?*")</f>
         <v/>
       </c>
@@ -3332,27 +3304,27 @@
       <c r="O24" s="23" t="n"/>
       <c r="P24" s="23" t="n"/>
       <c r="Q24" s="23" t="n"/>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>XR  Not ours</t>
-        </is>
-      </c>
-      <c r="V24" s="9" t="n"/>
-      <c r="W24" s="9" t="n"/>
-      <c r="X24" s="9" t="n"/>
-      <c r="Y24" s="9" t="n"/>
-      <c r="Z24" s="9" t="n"/>
-      <c r="AA24" s="9" t="n"/>
-      <c r="AB24" s="9" t="n"/>
-      <c r="AC24" s="9" t="n"/>
-      <c r="AD24" s="9" t="n"/>
-      <c r="AE24" s="9" t="n"/>
-      <c r="AF24" s="9" t="n"/>
-      <c r="AG24" s="9" t="n"/>
-      <c r="AH24" s="9" t="n"/>
-      <c r="AI24" s="9" t="n"/>
-      <c r="AJ24" s="9" t="n"/>
-      <c r="AL24" s="29">
+      <c r="U24" s="28" t="inlineStr">
+        <is>
+          <t>NOT OURS</t>
+        </is>
+      </c>
+      <c r="V24" s="23" t="n"/>
+      <c r="W24" s="23" t="n"/>
+      <c r="X24" s="23" t="n"/>
+      <c r="Y24" s="23" t="n"/>
+      <c r="Z24" s="23" t="n"/>
+      <c r="AA24" s="23" t="n"/>
+      <c r="AB24" s="23" t="n"/>
+      <c r="AC24" s="23" t="n"/>
+      <c r="AD24" s="23" t="n"/>
+      <c r="AE24" s="23" t="n"/>
+      <c r="AF24" s="23" t="n"/>
+      <c r="AG24" s="23" t="n"/>
+      <c r="AH24" s="23" t="n"/>
+      <c r="AI24" s="23" t="n"/>
+      <c r="AJ24" s="23" t="n"/>
+      <c r="AL24" s="30">
         <f>ROWS(tblLocations[LocationID])-COUNTIF(tblLocations[ItemCode],"?*")</f>
         <v/>
       </c>
@@ -3379,11 +3351,7 @@
       <c r="O25" s="23" t="n"/>
       <c r="P25" s="23" t="n"/>
       <c r="Q25" s="23" t="n"/>
-      <c r="U25" s="30" t="inlineStr">
-        <is>
-          <t>NOT OURS</t>
-        </is>
-      </c>
+      <c r="U25" s="23" t="n"/>
       <c r="V25" s="23" t="n"/>
       <c r="W25" s="23" t="n"/>
       <c r="X25" s="23" t="n"/>
@@ -3468,138 +3436,104 @@
       <c r="AI27" s="23" t="n"/>
       <c r="AJ27" s="23" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="23" t="n"/>
-      <c r="C28" s="23" t="n"/>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="23" t="n"/>
-      <c r="F28" s="23" t="n"/>
-      <c r="G28" s="23" t="n"/>
-      <c r="H28" s="23" t="n"/>
-      <c r="I28" s="23" t="n"/>
-      <c r="J28" s="23" t="n"/>
-      <c r="K28" s="23" t="n"/>
-      <c r="L28" s="23" t="n"/>
-      <c r="M28" s="23" t="n"/>
-      <c r="N28" s="23" t="n"/>
-      <c r="O28" s="23" t="n"/>
-      <c r="P28" s="23" t="n"/>
-      <c r="Q28" s="23" t="n"/>
-      <c r="U28" s="23" t="n"/>
-      <c r="V28" s="23" t="n"/>
-      <c r="W28" s="23" t="n"/>
-      <c r="X28" s="23" t="n"/>
-      <c r="Y28" s="23" t="n"/>
-      <c r="Z28" s="23" t="n"/>
-      <c r="AA28" s="23" t="n"/>
-      <c r="AB28" s="23" t="n"/>
-      <c r="AC28" s="23" t="n"/>
-      <c r="AD28" s="23" t="n"/>
-      <c r="AE28" s="23" t="n"/>
-      <c r="AF28" s="23" t="n"/>
-      <c r="AG28" s="23" t="n"/>
-      <c r="AH28" s="23" t="n"/>
-      <c r="AI28" s="23" t="n"/>
-      <c r="AJ28" s="23" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1"/>
-    <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="31" t="inlineStr">
+    <row r="28" ht="15" customHeight="1"/>
+    <row r="29" ht="15" customHeight="1">
+      <c r="B29" s="31" t="inlineStr">
         <is>
           <t>FIRE EXIT</t>
         </is>
       </c>
-      <c r="C30" s="32" t="n"/>
-      <c r="D30" s="32" t="n"/>
-      <c r="E30" s="32" t="n"/>
-      <c r="F30" s="32" t="n"/>
-      <c r="G30" s="32" t="n"/>
-      <c r="H30" s="32" t="n"/>
-      <c r="I30" s="32" t="n"/>
-      <c r="J30" s="32" t="n"/>
-      <c r="K30" s="32" t="n"/>
-      <c r="L30" s="32" t="n"/>
-      <c r="M30" s="32" t="n"/>
-      <c r="N30" s="32" t="n"/>
-      <c r="O30" s="32" t="n"/>
-      <c r="P30" s="32" t="n"/>
-      <c r="Q30" s="32" t="n"/>
-      <c r="R30" s="32" t="n"/>
-      <c r="S30" s="32" t="n"/>
-      <c r="T30" s="32" t="n"/>
-      <c r="U30" s="32" t="n"/>
-      <c r="V30" s="32" t="n"/>
-      <c r="W30" s="32" t="n"/>
-      <c r="X30" s="32" t="n"/>
-      <c r="Y30" s="32" t="n"/>
-      <c r="Z30" s="32" t="n"/>
-      <c r="AA30" s="32" t="n"/>
-      <c r="AB30" s="32" t="n"/>
-      <c r="AC30" s="32" t="n"/>
-      <c r="AD30" s="32" t="n"/>
-      <c r="AE30" s="32" t="n"/>
-      <c r="AF30" s="32" t="n"/>
-      <c r="AG30" s="32" t="n"/>
-      <c r="AH30" s="32" t="n"/>
-      <c r="AI30" s="32" t="n"/>
-      <c r="AJ30" s="32" t="n"/>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="32" t="n"/>
+      <c r="E29" s="32" t="n"/>
+      <c r="F29" s="32" t="n"/>
+      <c r="G29" s="32" t="n"/>
+      <c r="H29" s="32" t="n"/>
+      <c r="I29" s="32" t="n"/>
+      <c r="J29" s="32" t="n"/>
+      <c r="K29" s="32" t="n"/>
+      <c r="L29" s="32" t="n"/>
+      <c r="M29" s="32" t="n"/>
+      <c r="N29" s="32" t="n"/>
+      <c r="O29" s="32" t="n"/>
+      <c r="P29" s="32" t="n"/>
+      <c r="Q29" s="32" t="n"/>
+      <c r="R29" s="32" t="n"/>
+      <c r="S29" s="32" t="n"/>
+      <c r="T29" s="32" t="n"/>
+      <c r="U29" s="32" t="n"/>
+      <c r="V29" s="32" t="n"/>
+      <c r="W29" s="32" t="n"/>
+      <c r="X29" s="32" t="n"/>
+      <c r="Y29" s="32" t="n"/>
+      <c r="Z29" s="32" t="n"/>
+      <c r="AA29" s="32" t="n"/>
+      <c r="AB29" s="32" t="n"/>
+      <c r="AC29" s="32" t="n"/>
+      <c r="AD29" s="32" t="n"/>
+      <c r="AE29" s="32" t="n"/>
+      <c r="AF29" s="32" t="n"/>
+      <c r="AG29" s="32" t="n"/>
+      <c r="AH29" s="32" t="n"/>
+      <c r="AI29" s="32" t="n"/>
+      <c r="AJ29" s="32" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="R6:T28"/>
     <mergeCell ref="AO10:AU10"/>
     <mergeCell ref="AP1:AU1"/>
-    <mergeCell ref="U24:AJ24"/>
     <mergeCell ref="AO22:AU22"/>
     <mergeCell ref="AO9:AU9"/>
     <mergeCell ref="B4:AJ4"/>
+    <mergeCell ref="B22:Q27"/>
+    <mergeCell ref="B6:Q6"/>
+    <mergeCell ref="U23:AJ23"/>
     <mergeCell ref="AL24:AN24"/>
+    <mergeCell ref="R6:T27"/>
     <mergeCell ref="A1:AO1"/>
     <mergeCell ref="AL23:AN23"/>
     <mergeCell ref="AO17:AU17"/>
     <mergeCell ref="AO8:AU8"/>
+    <mergeCell ref="B16:Q16"/>
     <mergeCell ref="AL6:AU6"/>
-    <mergeCell ref="B7:Q7"/>
     <mergeCell ref="AO16:AU16"/>
     <mergeCell ref="AO7:AU7"/>
     <mergeCell ref="U6:AJ6"/>
-    <mergeCell ref="U25:AJ28"/>
     <mergeCell ref="AO23:AU23"/>
-    <mergeCell ref="B22:Q22"/>
-    <mergeCell ref="B23:Q28"/>
     <mergeCell ref="AO13:AU13"/>
-    <mergeCell ref="B12:Q12"/>
     <mergeCell ref="AL22:AN22"/>
+    <mergeCell ref="B21:Q21"/>
+    <mergeCell ref="B11:Q11"/>
+    <mergeCell ref="B29:AJ29"/>
     <mergeCell ref="U11:AJ11"/>
     <mergeCell ref="AO19:AU19"/>
     <mergeCell ref="AO15:AU15"/>
+    <mergeCell ref="U24:AJ27"/>
     <mergeCell ref="A2:AU2"/>
     <mergeCell ref="U16:AJ16"/>
     <mergeCell ref="AO24:AU24"/>
     <mergeCell ref="AO18:AU18"/>
     <mergeCell ref="AO14:AU14"/>
-    <mergeCell ref="B17:Q17"/>
     <mergeCell ref="AL21:AU21"/>
     <mergeCell ref="AL12:AU12"/>
-    <mergeCell ref="B30:AJ30"/>
     <mergeCell ref="U21:AJ21"/>
   </mergeCells>
-  <conditionalFormatting sqref="B18:Q21">
+  <conditionalFormatting sqref="B17:Q20">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>LEN(B18)&gt;0</formula>
+      <formula>LEN(B17)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13:Q16">
+  <conditionalFormatting sqref="B12:Q15">
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>LEN(B13)&gt;0</formula>
+      <formula>LEN(B12)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:Q11">
+  <conditionalFormatting sqref="B7:Q10">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>LEN(B8)&gt;0</formula>
+      <formula>LEN(B7)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U22:AJ23">
+  <conditionalFormatting sqref="U22:AJ22">
     <cfRule type="expression" priority="4" dxfId="1">
       <formula>LEN(U22)&gt;0</formula>
     </cfRule>
@@ -7611,7 +7545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I420"/>
+  <dimension ref="A1:I404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7728,7 +7662,7 @@
       <c r="F5" s="58" t="n"/>
       <c r="G5" s="58" t="n"/>
       <c r="H5" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I5" s="60" t="n">
         <v>17</v>
@@ -7761,7 +7695,7 @@
       <c r="F6" s="58" t="n"/>
       <c r="G6" s="58" t="n"/>
       <c r="H6" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I6" s="60" t="n">
         <v>16</v>
@@ -7794,7 +7728,7 @@
       <c r="F7" s="58" t="n"/>
       <c r="G7" s="58" t="n"/>
       <c r="H7" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I7" s="60" t="n">
         <v>15</v>
@@ -7827,7 +7761,7 @@
       <c r="F8" s="58" t="n"/>
       <c r="G8" s="58" t="n"/>
       <c r="H8" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I8" s="60" t="n">
         <v>14</v>
@@ -7860,7 +7794,7 @@
       <c r="F9" s="58" t="n"/>
       <c r="G9" s="58" t="n"/>
       <c r="H9" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I9" s="60" t="n">
         <v>13</v>
@@ -7893,7 +7827,7 @@
       <c r="F10" s="58" t="n"/>
       <c r="G10" s="58" t="n"/>
       <c r="H10" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I10" s="60" t="n">
         <v>12</v>
@@ -7926,7 +7860,7 @@
       <c r="F11" s="58" t="n"/>
       <c r="G11" s="58" t="n"/>
       <c r="H11" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I11" s="60" t="n">
         <v>11</v>
@@ -7959,7 +7893,7 @@
       <c r="F12" s="58" t="n"/>
       <c r="G12" s="58" t="n"/>
       <c r="H12" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I12" s="60" t="n">
         <v>10</v>
@@ -7992,7 +7926,7 @@
       <c r="F13" s="58" t="n"/>
       <c r="G13" s="58" t="n"/>
       <c r="H13" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I13" s="60" t="n">
         <v>9</v>
@@ -8025,7 +7959,7 @@
       <c r="F14" s="58" t="n"/>
       <c r="G14" s="58" t="n"/>
       <c r="H14" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I14" s="60" t="n">
         <v>8</v>
@@ -8058,7 +7992,7 @@
       <c r="F15" s="58" t="n"/>
       <c r="G15" s="58" t="n"/>
       <c r="H15" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I15" s="60" t="n">
         <v>7</v>
@@ -8091,7 +8025,7 @@
       <c r="F16" s="58" t="n"/>
       <c r="G16" s="58" t="n"/>
       <c r="H16" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I16" s="60" t="n">
         <v>6</v>
@@ -8124,7 +8058,7 @@
       <c r="F17" s="58" t="n"/>
       <c r="G17" s="58" t="n"/>
       <c r="H17" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I17" s="60" t="n">
         <v>5</v>
@@ -8157,7 +8091,7 @@
       <c r="F18" s="58" t="n"/>
       <c r="G18" s="58" t="n"/>
       <c r="H18" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I18" s="60" t="n">
         <v>4</v>
@@ -8190,7 +8124,7 @@
       <c r="F19" s="58" t="n"/>
       <c r="G19" s="58" t="n"/>
       <c r="H19" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I19" s="60" t="n">
         <v>3</v>
@@ -8223,7 +8157,7 @@
       <c r="F20" s="58" t="n"/>
       <c r="G20" s="58" t="n"/>
       <c r="H20" s="60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I20" s="60" t="n">
         <v>2</v>
@@ -8256,7 +8190,7 @@
       <c r="F21" s="58" t="n"/>
       <c r="G21" s="58" t="n"/>
       <c r="H21" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I21" s="60" t="n">
         <v>17</v>
@@ -8289,7 +8223,7 @@
       <c r="F22" s="58" t="n"/>
       <c r="G22" s="58" t="n"/>
       <c r="H22" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I22" s="60" t="n">
         <v>16</v>
@@ -8322,7 +8256,7 @@
       <c r="F23" s="58" t="n"/>
       <c r="G23" s="58" t="n"/>
       <c r="H23" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I23" s="60" t="n">
         <v>15</v>
@@ -8355,7 +8289,7 @@
       <c r="F24" s="58" t="n"/>
       <c r="G24" s="58" t="n"/>
       <c r="H24" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I24" s="60" t="n">
         <v>14</v>
@@ -8388,7 +8322,7 @@
       <c r="F25" s="58" t="n"/>
       <c r="G25" s="58" t="n"/>
       <c r="H25" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I25" s="60" t="n">
         <v>13</v>
@@ -8421,7 +8355,7 @@
       <c r="F26" s="58" t="n"/>
       <c r="G26" s="58" t="n"/>
       <c r="H26" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I26" s="60" t="n">
         <v>12</v>
@@ -8454,7 +8388,7 @@
       <c r="F27" s="58" t="n"/>
       <c r="G27" s="58" t="n"/>
       <c r="H27" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I27" s="60" t="n">
         <v>11</v>
@@ -8487,7 +8421,7 @@
       <c r="F28" s="58" t="n"/>
       <c r="G28" s="58" t="n"/>
       <c r="H28" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I28" s="60" t="n">
         <v>10</v>
@@ -8520,7 +8454,7 @@
       <c r="F29" s="58" t="n"/>
       <c r="G29" s="58" t="n"/>
       <c r="H29" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I29" s="60" t="n">
         <v>9</v>
@@ -8553,7 +8487,7 @@
       <c r="F30" s="58" t="n"/>
       <c r="G30" s="58" t="n"/>
       <c r="H30" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I30" s="60" t="n">
         <v>8</v>
@@ -8586,7 +8520,7 @@
       <c r="F31" s="58" t="n"/>
       <c r="G31" s="58" t="n"/>
       <c r="H31" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I31" s="60" t="n">
         <v>7</v>
@@ -8619,7 +8553,7 @@
       <c r="F32" s="58" t="n"/>
       <c r="G32" s="58" t="n"/>
       <c r="H32" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I32" s="60" t="n">
         <v>6</v>
@@ -8652,7 +8586,7 @@
       <c r="F33" s="58" t="n"/>
       <c r="G33" s="58" t="n"/>
       <c r="H33" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I33" s="60" t="n">
         <v>5</v>
@@ -8685,7 +8619,7 @@
       <c r="F34" s="58" t="n"/>
       <c r="G34" s="58" t="n"/>
       <c r="H34" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I34" s="60" t="n">
         <v>4</v>
@@ -8718,7 +8652,7 @@
       <c r="F35" s="58" t="n"/>
       <c r="G35" s="58" t="n"/>
       <c r="H35" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I35" s="60" t="n">
         <v>3</v>
@@ -8751,7 +8685,7 @@
       <c r="F36" s="58" t="n"/>
       <c r="G36" s="58" t="n"/>
       <c r="H36" s="60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I36" s="60" t="n">
         <v>2</v>
@@ -8784,7 +8718,7 @@
       <c r="F37" s="58" t="n"/>
       <c r="G37" s="58" t="n"/>
       <c r="H37" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I37" s="60" t="n">
         <v>17</v>
@@ -8817,7 +8751,7 @@
       <c r="F38" s="58" t="n"/>
       <c r="G38" s="58" t="n"/>
       <c r="H38" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I38" s="60" t="n">
         <v>16</v>
@@ -8850,7 +8784,7 @@
       <c r="F39" s="58" t="n"/>
       <c r="G39" s="58" t="n"/>
       <c r="H39" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I39" s="60" t="n">
         <v>15</v>
@@ -8883,7 +8817,7 @@
       <c r="F40" s="58" t="n"/>
       <c r="G40" s="58" t="n"/>
       <c r="H40" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I40" s="60" t="n">
         <v>14</v>
@@ -8916,7 +8850,7 @@
       <c r="F41" s="58" t="n"/>
       <c r="G41" s="58" t="n"/>
       <c r="H41" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I41" s="60" t="n">
         <v>13</v>
@@ -8949,7 +8883,7 @@
       <c r="F42" s="58" t="n"/>
       <c r="G42" s="58" t="n"/>
       <c r="H42" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I42" s="60" t="n">
         <v>12</v>
@@ -8982,7 +8916,7 @@
       <c r="F43" s="58" t="n"/>
       <c r="G43" s="58" t="n"/>
       <c r="H43" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I43" s="60" t="n">
         <v>11</v>
@@ -9015,7 +8949,7 @@
       <c r="F44" s="58" t="n"/>
       <c r="G44" s="58" t="n"/>
       <c r="H44" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I44" s="60" t="n">
         <v>10</v>
@@ -9048,7 +8982,7 @@
       <c r="F45" s="58" t="n"/>
       <c r="G45" s="58" t="n"/>
       <c r="H45" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I45" s="60" t="n">
         <v>9</v>
@@ -9081,7 +9015,7 @@
       <c r="F46" s="58" t="n"/>
       <c r="G46" s="58" t="n"/>
       <c r="H46" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I46" s="60" t="n">
         <v>8</v>
@@ -9114,7 +9048,7 @@
       <c r="F47" s="58" t="n"/>
       <c r="G47" s="58" t="n"/>
       <c r="H47" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I47" s="60" t="n">
         <v>7</v>
@@ -9147,7 +9081,7 @@
       <c r="F48" s="58" t="n"/>
       <c r="G48" s="58" t="n"/>
       <c r="H48" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I48" s="60" t="n">
         <v>6</v>
@@ -9180,7 +9114,7 @@
       <c r="F49" s="58" t="n"/>
       <c r="G49" s="58" t="n"/>
       <c r="H49" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I49" s="60" t="n">
         <v>5</v>
@@ -9213,7 +9147,7 @@
       <c r="F50" s="58" t="n"/>
       <c r="G50" s="58" t="n"/>
       <c r="H50" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I50" s="60" t="n">
         <v>4</v>
@@ -9246,7 +9180,7 @@
       <c r="F51" s="58" t="n"/>
       <c r="G51" s="58" t="n"/>
       <c r="H51" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I51" s="60" t="n">
         <v>3</v>
@@ -9279,7 +9213,7 @@
       <c r="F52" s="58" t="n"/>
       <c r="G52" s="58" t="n"/>
       <c r="H52" s="60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I52" s="60" t="n">
         <v>2</v>
@@ -9312,7 +9246,7 @@
       <c r="F53" s="58" t="n"/>
       <c r="G53" s="58" t="n"/>
       <c r="H53" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I53" s="60" t="n">
         <v>17</v>
@@ -9345,7 +9279,7 @@
       <c r="F54" s="58" t="n"/>
       <c r="G54" s="58" t="n"/>
       <c r="H54" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I54" s="60" t="n">
         <v>16</v>
@@ -9378,7 +9312,7 @@
       <c r="F55" s="58" t="n"/>
       <c r="G55" s="58" t="n"/>
       <c r="H55" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I55" s="60" t="n">
         <v>15</v>
@@ -9411,7 +9345,7 @@
       <c r="F56" s="58" t="n"/>
       <c r="G56" s="58" t="n"/>
       <c r="H56" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I56" s="60" t="n">
         <v>14</v>
@@ -9444,7 +9378,7 @@
       <c r="F57" s="58" t="n"/>
       <c r="G57" s="58" t="n"/>
       <c r="H57" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I57" s="60" t="n">
         <v>13</v>
@@ -9477,7 +9411,7 @@
       <c r="F58" s="58" t="n"/>
       <c r="G58" s="58" t="n"/>
       <c r="H58" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I58" s="60" t="n">
         <v>12</v>
@@ -9510,7 +9444,7 @@
       <c r="F59" s="58" t="n"/>
       <c r="G59" s="58" t="n"/>
       <c r="H59" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I59" s="60" t="n">
         <v>11</v>
@@ -9543,7 +9477,7 @@
       <c r="F60" s="58" t="n"/>
       <c r="G60" s="58" t="n"/>
       <c r="H60" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I60" s="60" t="n">
         <v>10</v>
@@ -9576,7 +9510,7 @@
       <c r="F61" s="58" t="n"/>
       <c r="G61" s="58" t="n"/>
       <c r="H61" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I61" s="60" t="n">
         <v>9</v>
@@ -9609,7 +9543,7 @@
       <c r="F62" s="58" t="n"/>
       <c r="G62" s="58" t="n"/>
       <c r="H62" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I62" s="60" t="n">
         <v>8</v>
@@ -9642,7 +9576,7 @@
       <c r="F63" s="58" t="n"/>
       <c r="G63" s="58" t="n"/>
       <c r="H63" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I63" s="60" t="n">
         <v>7</v>
@@ -9675,7 +9609,7 @@
       <c r="F64" s="58" t="n"/>
       <c r="G64" s="58" t="n"/>
       <c r="H64" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I64" s="60" t="n">
         <v>6</v>
@@ -9708,7 +9642,7 @@
       <c r="F65" s="58" t="n"/>
       <c r="G65" s="58" t="n"/>
       <c r="H65" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I65" s="60" t="n">
         <v>5</v>
@@ -9741,7 +9675,7 @@
       <c r="F66" s="58" t="n"/>
       <c r="G66" s="58" t="n"/>
       <c r="H66" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I66" s="60" t="n">
         <v>4</v>
@@ -9774,7 +9708,7 @@
       <c r="F67" s="58" t="n"/>
       <c r="G67" s="58" t="n"/>
       <c r="H67" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I67" s="60" t="n">
         <v>3</v>
@@ -9807,7 +9741,7 @@
       <c r="F68" s="58" t="n"/>
       <c r="G68" s="58" t="n"/>
       <c r="H68" s="60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I68" s="60" t="n">
         <v>2</v>
@@ -9840,7 +9774,7 @@
       <c r="F69" s="58" t="n"/>
       <c r="G69" s="58" t="n"/>
       <c r="H69" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I69" s="60" t="n">
         <v>17</v>
@@ -9873,7 +9807,7 @@
       <c r="F70" s="58" t="n"/>
       <c r="G70" s="58" t="n"/>
       <c r="H70" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I70" s="60" t="n">
         <v>16</v>
@@ -9906,7 +9840,7 @@
       <c r="F71" s="58" t="n"/>
       <c r="G71" s="58" t="n"/>
       <c r="H71" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I71" s="60" t="n">
         <v>15</v>
@@ -9939,7 +9873,7 @@
       <c r="F72" s="58" t="n"/>
       <c r="G72" s="58" t="n"/>
       <c r="H72" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I72" s="60" t="n">
         <v>14</v>
@@ -9972,7 +9906,7 @@
       <c r="F73" s="58" t="n"/>
       <c r="G73" s="58" t="n"/>
       <c r="H73" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I73" s="60" t="n">
         <v>13</v>
@@ -10005,7 +9939,7 @@
       <c r="F74" s="58" t="n"/>
       <c r="G74" s="58" t="n"/>
       <c r="H74" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I74" s="60" t="n">
         <v>12</v>
@@ -10038,7 +9972,7 @@
       <c r="F75" s="58" t="n"/>
       <c r="G75" s="58" t="n"/>
       <c r="H75" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I75" s="60" t="n">
         <v>11</v>
@@ -10071,7 +10005,7 @@
       <c r="F76" s="58" t="n"/>
       <c r="G76" s="58" t="n"/>
       <c r="H76" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I76" s="60" t="n">
         <v>10</v>
@@ -10104,7 +10038,7 @@
       <c r="F77" s="58" t="n"/>
       <c r="G77" s="58" t="n"/>
       <c r="H77" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I77" s="60" t="n">
         <v>9</v>
@@ -10137,7 +10071,7 @@
       <c r="F78" s="58" t="n"/>
       <c r="G78" s="58" t="n"/>
       <c r="H78" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I78" s="60" t="n">
         <v>8</v>
@@ -10170,7 +10104,7 @@
       <c r="F79" s="58" t="n"/>
       <c r="G79" s="58" t="n"/>
       <c r="H79" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I79" s="60" t="n">
         <v>7</v>
@@ -10203,7 +10137,7 @@
       <c r="F80" s="58" t="n"/>
       <c r="G80" s="58" t="n"/>
       <c r="H80" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I80" s="60" t="n">
         <v>6</v>
@@ -10236,7 +10170,7 @@
       <c r="F81" s="58" t="n"/>
       <c r="G81" s="58" t="n"/>
       <c r="H81" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I81" s="60" t="n">
         <v>5</v>
@@ -10269,7 +10203,7 @@
       <c r="F82" s="58" t="n"/>
       <c r="G82" s="58" t="n"/>
       <c r="H82" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I82" s="60" t="n">
         <v>4</v>
@@ -10302,7 +10236,7 @@
       <c r="F83" s="58" t="n"/>
       <c r="G83" s="58" t="n"/>
       <c r="H83" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I83" s="60" t="n">
         <v>3</v>
@@ -10335,7 +10269,7 @@
       <c r="F84" s="58" t="n"/>
       <c r="G84" s="58" t="n"/>
       <c r="H84" s="60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I84" s="60" t="n">
         <v>2</v>
@@ -10368,7 +10302,7 @@
       <c r="F85" s="58" t="n"/>
       <c r="G85" s="58" t="n"/>
       <c r="H85" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I85" s="60" t="n">
         <v>17</v>
@@ -10401,7 +10335,7 @@
       <c r="F86" s="58" t="n"/>
       <c r="G86" s="58" t="n"/>
       <c r="H86" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I86" s="60" t="n">
         <v>16</v>
@@ -10434,7 +10368,7 @@
       <c r="F87" s="58" t="n"/>
       <c r="G87" s="58" t="n"/>
       <c r="H87" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I87" s="60" t="n">
         <v>15</v>
@@ -10467,7 +10401,7 @@
       <c r="F88" s="58" t="n"/>
       <c r="G88" s="58" t="n"/>
       <c r="H88" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I88" s="60" t="n">
         <v>14</v>
@@ -10500,7 +10434,7 @@
       <c r="F89" s="58" t="n"/>
       <c r="G89" s="58" t="n"/>
       <c r="H89" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I89" s="60" t="n">
         <v>13</v>
@@ -10533,7 +10467,7 @@
       <c r="F90" s="58" t="n"/>
       <c r="G90" s="58" t="n"/>
       <c r="H90" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I90" s="60" t="n">
         <v>12</v>
@@ -10566,7 +10500,7 @@
       <c r="F91" s="58" t="n"/>
       <c r="G91" s="58" t="n"/>
       <c r="H91" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I91" s="60" t="n">
         <v>11</v>
@@ -10599,7 +10533,7 @@
       <c r="F92" s="58" t="n"/>
       <c r="G92" s="58" t="n"/>
       <c r="H92" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I92" s="60" t="n">
         <v>10</v>
@@ -10632,7 +10566,7 @@
       <c r="F93" s="58" t="n"/>
       <c r="G93" s="58" t="n"/>
       <c r="H93" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I93" s="60" t="n">
         <v>9</v>
@@ -10665,7 +10599,7 @@
       <c r="F94" s="58" t="n"/>
       <c r="G94" s="58" t="n"/>
       <c r="H94" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I94" s="60" t="n">
         <v>8</v>
@@ -10698,7 +10632,7 @@
       <c r="F95" s="58" t="n"/>
       <c r="G95" s="58" t="n"/>
       <c r="H95" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I95" s="60" t="n">
         <v>7</v>
@@ -10731,7 +10665,7 @@
       <c r="F96" s="58" t="n"/>
       <c r="G96" s="58" t="n"/>
       <c r="H96" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I96" s="60" t="n">
         <v>6</v>
@@ -10764,7 +10698,7 @@
       <c r="F97" s="58" t="n"/>
       <c r="G97" s="58" t="n"/>
       <c r="H97" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I97" s="60" t="n">
         <v>5</v>
@@ -10797,7 +10731,7 @@
       <c r="F98" s="58" t="n"/>
       <c r="G98" s="58" t="n"/>
       <c r="H98" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I98" s="60" t="n">
         <v>4</v>
@@ -10830,7 +10764,7 @@
       <c r="F99" s="58" t="n"/>
       <c r="G99" s="58" t="n"/>
       <c r="H99" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I99" s="60" t="n">
         <v>3</v>
@@ -10863,7 +10797,7 @@
       <c r="F100" s="58" t="n"/>
       <c r="G100" s="58" t="n"/>
       <c r="H100" s="60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I100" s="60" t="n">
         <v>2</v>
@@ -10896,7 +10830,7 @@
       <c r="F101" s="58" t="n"/>
       <c r="G101" s="58" t="n"/>
       <c r="H101" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I101" s="60" t="n">
         <v>17</v>
@@ -10929,7 +10863,7 @@
       <c r="F102" s="58" t="n"/>
       <c r="G102" s="58" t="n"/>
       <c r="H102" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I102" s="60" t="n">
         <v>16</v>
@@ -10962,7 +10896,7 @@
       <c r="F103" s="58" t="n"/>
       <c r="G103" s="58" t="n"/>
       <c r="H103" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I103" s="60" t="n">
         <v>15</v>
@@ -10995,7 +10929,7 @@
       <c r="F104" s="58" t="n"/>
       <c r="G104" s="58" t="n"/>
       <c r="H104" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I104" s="60" t="n">
         <v>14</v>
@@ -11028,7 +10962,7 @@
       <c r="F105" s="58" t="n"/>
       <c r="G105" s="58" t="n"/>
       <c r="H105" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I105" s="60" t="n">
         <v>13</v>
@@ -11061,7 +10995,7 @@
       <c r="F106" s="58" t="n"/>
       <c r="G106" s="58" t="n"/>
       <c r="H106" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I106" s="60" t="n">
         <v>12</v>
@@ -11094,7 +11028,7 @@
       <c r="F107" s="58" t="n"/>
       <c r="G107" s="58" t="n"/>
       <c r="H107" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I107" s="60" t="n">
         <v>11</v>
@@ -11127,7 +11061,7 @@
       <c r="F108" s="58" t="n"/>
       <c r="G108" s="58" t="n"/>
       <c r="H108" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I108" s="60" t="n">
         <v>10</v>
@@ -11160,7 +11094,7 @@
       <c r="F109" s="58" t="n"/>
       <c r="G109" s="58" t="n"/>
       <c r="H109" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I109" s="60" t="n">
         <v>9</v>
@@ -11193,7 +11127,7 @@
       <c r="F110" s="58" t="n"/>
       <c r="G110" s="58" t="n"/>
       <c r="H110" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I110" s="60" t="n">
         <v>8</v>
@@ -11226,7 +11160,7 @@
       <c r="F111" s="58" t="n"/>
       <c r="G111" s="58" t="n"/>
       <c r="H111" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I111" s="60" t="n">
         <v>7</v>
@@ -11259,7 +11193,7 @@
       <c r="F112" s="58" t="n"/>
       <c r="G112" s="58" t="n"/>
       <c r="H112" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I112" s="60" t="n">
         <v>6</v>
@@ -11292,7 +11226,7 @@
       <c r="F113" s="58" t="n"/>
       <c r="G113" s="58" t="n"/>
       <c r="H113" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I113" s="60" t="n">
         <v>5</v>
@@ -11325,7 +11259,7 @@
       <c r="F114" s="58" t="n"/>
       <c r="G114" s="58" t="n"/>
       <c r="H114" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I114" s="60" t="n">
         <v>4</v>
@@ -11358,7 +11292,7 @@
       <c r="F115" s="58" t="n"/>
       <c r="G115" s="58" t="n"/>
       <c r="H115" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I115" s="60" t="n">
         <v>3</v>
@@ -11391,7 +11325,7 @@
       <c r="F116" s="58" t="n"/>
       <c r="G116" s="58" t="n"/>
       <c r="H116" s="60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I116" s="60" t="n">
         <v>2</v>
@@ -11424,7 +11358,7 @@
       <c r="F117" s="58" t="n"/>
       <c r="G117" s="58" t="n"/>
       <c r="H117" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I117" s="60" t="n">
         <v>17</v>
@@ -11457,7 +11391,7 @@
       <c r="F118" s="58" t="n"/>
       <c r="G118" s="58" t="n"/>
       <c r="H118" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I118" s="60" t="n">
         <v>16</v>
@@ -11490,7 +11424,7 @@
       <c r="F119" s="58" t="n"/>
       <c r="G119" s="58" t="n"/>
       <c r="H119" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I119" s="60" t="n">
         <v>15</v>
@@ -11523,7 +11457,7 @@
       <c r="F120" s="58" t="n"/>
       <c r="G120" s="58" t="n"/>
       <c r="H120" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I120" s="60" t="n">
         <v>14</v>
@@ -11556,7 +11490,7 @@
       <c r="F121" s="58" t="n"/>
       <c r="G121" s="58" t="n"/>
       <c r="H121" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I121" s="60" t="n">
         <v>13</v>
@@ -11589,7 +11523,7 @@
       <c r="F122" s="58" t="n"/>
       <c r="G122" s="58" t="n"/>
       <c r="H122" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I122" s="60" t="n">
         <v>12</v>
@@ -11622,7 +11556,7 @@
       <c r="F123" s="58" t="n"/>
       <c r="G123" s="58" t="n"/>
       <c r="H123" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I123" s="60" t="n">
         <v>11</v>
@@ -11655,7 +11589,7 @@
       <c r="F124" s="58" t="n"/>
       <c r="G124" s="58" t="n"/>
       <c r="H124" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I124" s="60" t="n">
         <v>10</v>
@@ -11688,7 +11622,7 @@
       <c r="F125" s="58" t="n"/>
       <c r="G125" s="58" t="n"/>
       <c r="H125" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I125" s="60" t="n">
         <v>9</v>
@@ -11721,7 +11655,7 @@
       <c r="F126" s="58" t="n"/>
       <c r="G126" s="58" t="n"/>
       <c r="H126" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I126" s="60" t="n">
         <v>8</v>
@@ -11754,7 +11688,7 @@
       <c r="F127" s="58" t="n"/>
       <c r="G127" s="58" t="n"/>
       <c r="H127" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I127" s="60" t="n">
         <v>7</v>
@@ -11787,7 +11721,7 @@
       <c r="F128" s="58" t="n"/>
       <c r="G128" s="58" t="n"/>
       <c r="H128" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I128" s="60" t="n">
         <v>6</v>
@@ -11820,7 +11754,7 @@
       <c r="F129" s="58" t="n"/>
       <c r="G129" s="58" t="n"/>
       <c r="H129" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I129" s="60" t="n">
         <v>5</v>
@@ -11853,7 +11787,7 @@
       <c r="F130" s="58" t="n"/>
       <c r="G130" s="58" t="n"/>
       <c r="H130" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I130" s="60" t="n">
         <v>4</v>
@@ -11886,7 +11820,7 @@
       <c r="F131" s="58" t="n"/>
       <c r="G131" s="58" t="n"/>
       <c r="H131" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I131" s="60" t="n">
         <v>3</v>
@@ -11919,7 +11853,7 @@
       <c r="F132" s="58" t="n"/>
       <c r="G132" s="58" t="n"/>
       <c r="H132" s="60" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I132" s="60" t="n">
         <v>2</v>
@@ -11952,7 +11886,7 @@
       <c r="F133" s="58" t="n"/>
       <c r="G133" s="58" t="n"/>
       <c r="H133" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I133" s="60" t="n">
         <v>17</v>
@@ -11985,7 +11919,7 @@
       <c r="F134" s="58" t="n"/>
       <c r="G134" s="58" t="n"/>
       <c r="H134" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I134" s="60" t="n">
         <v>16</v>
@@ -12018,7 +11952,7 @@
       <c r="F135" s="58" t="n"/>
       <c r="G135" s="58" t="n"/>
       <c r="H135" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I135" s="60" t="n">
         <v>15</v>
@@ -12051,7 +11985,7 @@
       <c r="F136" s="58" t="n"/>
       <c r="G136" s="58" t="n"/>
       <c r="H136" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I136" s="60" t="n">
         <v>14</v>
@@ -12084,7 +12018,7 @@
       <c r="F137" s="58" t="n"/>
       <c r="G137" s="58" t="n"/>
       <c r="H137" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I137" s="60" t="n">
         <v>13</v>
@@ -12117,7 +12051,7 @@
       <c r="F138" s="58" t="n"/>
       <c r="G138" s="58" t="n"/>
       <c r="H138" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I138" s="60" t="n">
         <v>12</v>
@@ -12150,7 +12084,7 @@
       <c r="F139" s="58" t="n"/>
       <c r="G139" s="58" t="n"/>
       <c r="H139" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I139" s="60" t="n">
         <v>11</v>
@@ -12183,7 +12117,7 @@
       <c r="F140" s="58" t="n"/>
       <c r="G140" s="58" t="n"/>
       <c r="H140" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I140" s="60" t="n">
         <v>10</v>
@@ -12216,7 +12150,7 @@
       <c r="F141" s="58" t="n"/>
       <c r="G141" s="58" t="n"/>
       <c r="H141" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I141" s="60" t="n">
         <v>9</v>
@@ -12249,7 +12183,7 @@
       <c r="F142" s="58" t="n"/>
       <c r="G142" s="58" t="n"/>
       <c r="H142" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I142" s="60" t="n">
         <v>8</v>
@@ -12282,7 +12216,7 @@
       <c r="F143" s="58" t="n"/>
       <c r="G143" s="58" t="n"/>
       <c r="H143" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I143" s="60" t="n">
         <v>7</v>
@@ -12315,7 +12249,7 @@
       <c r="F144" s="58" t="n"/>
       <c r="G144" s="58" t="n"/>
       <c r="H144" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I144" s="60" t="n">
         <v>6</v>
@@ -12348,7 +12282,7 @@
       <c r="F145" s="58" t="n"/>
       <c r="G145" s="58" t="n"/>
       <c r="H145" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I145" s="60" t="n">
         <v>5</v>
@@ -12381,7 +12315,7 @@
       <c r="F146" s="58" t="n"/>
       <c r="G146" s="58" t="n"/>
       <c r="H146" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I146" s="60" t="n">
         <v>4</v>
@@ -12414,7 +12348,7 @@
       <c r="F147" s="58" t="n"/>
       <c r="G147" s="58" t="n"/>
       <c r="H147" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I147" s="60" t="n">
         <v>3</v>
@@ -12447,7 +12381,7 @@
       <c r="F148" s="58" t="n"/>
       <c r="G148" s="58" t="n"/>
       <c r="H148" s="60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I148" s="60" t="n">
         <v>2</v>
@@ -12480,7 +12414,7 @@
       <c r="F149" s="58" t="n"/>
       <c r="G149" s="58" t="n"/>
       <c r="H149" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I149" s="60" t="n">
         <v>17</v>
@@ -12513,7 +12447,7 @@
       <c r="F150" s="58" t="n"/>
       <c r="G150" s="58" t="n"/>
       <c r="H150" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I150" s="60" t="n">
         <v>16</v>
@@ -12546,7 +12480,7 @@
       <c r="F151" s="58" t="n"/>
       <c r="G151" s="58" t="n"/>
       <c r="H151" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I151" s="60" t="n">
         <v>15</v>
@@ -12579,7 +12513,7 @@
       <c r="F152" s="58" t="n"/>
       <c r="G152" s="58" t="n"/>
       <c r="H152" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I152" s="60" t="n">
         <v>14</v>
@@ -12612,7 +12546,7 @@
       <c r="F153" s="58" t="n"/>
       <c r="G153" s="58" t="n"/>
       <c r="H153" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I153" s="60" t="n">
         <v>13</v>
@@ -12645,7 +12579,7 @@
       <c r="F154" s="58" t="n"/>
       <c r="G154" s="58" t="n"/>
       <c r="H154" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I154" s="60" t="n">
         <v>12</v>
@@ -12678,7 +12612,7 @@
       <c r="F155" s="58" t="n"/>
       <c r="G155" s="58" t="n"/>
       <c r="H155" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I155" s="60" t="n">
         <v>11</v>
@@ -12711,7 +12645,7 @@
       <c r="F156" s="58" t="n"/>
       <c r="G156" s="58" t="n"/>
       <c r="H156" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I156" s="60" t="n">
         <v>10</v>
@@ -12744,7 +12678,7 @@
       <c r="F157" s="58" t="n"/>
       <c r="G157" s="58" t="n"/>
       <c r="H157" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I157" s="60" t="n">
         <v>9</v>
@@ -12777,7 +12711,7 @@
       <c r="F158" s="58" t="n"/>
       <c r="G158" s="58" t="n"/>
       <c r="H158" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I158" s="60" t="n">
         <v>8</v>
@@ -12810,7 +12744,7 @@
       <c r="F159" s="58" t="n"/>
       <c r="G159" s="58" t="n"/>
       <c r="H159" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I159" s="60" t="n">
         <v>7</v>
@@ -12843,7 +12777,7 @@
       <c r="F160" s="58" t="n"/>
       <c r="G160" s="58" t="n"/>
       <c r="H160" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I160" s="60" t="n">
         <v>6</v>
@@ -12876,7 +12810,7 @@
       <c r="F161" s="58" t="n"/>
       <c r="G161" s="58" t="n"/>
       <c r="H161" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I161" s="60" t="n">
         <v>5</v>
@@ -12909,7 +12843,7 @@
       <c r="F162" s="58" t="n"/>
       <c r="G162" s="58" t="n"/>
       <c r="H162" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I162" s="60" t="n">
         <v>4</v>
@@ -12942,7 +12876,7 @@
       <c r="F163" s="58" t="n"/>
       <c r="G163" s="58" t="n"/>
       <c r="H163" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I163" s="60" t="n">
         <v>3</v>
@@ -12975,7 +12909,7 @@
       <c r="F164" s="58" t="n"/>
       <c r="G164" s="58" t="n"/>
       <c r="H164" s="60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I164" s="60" t="n">
         <v>2</v>
@@ -13008,7 +12942,7 @@
       <c r="F165" s="58" t="n"/>
       <c r="G165" s="58" t="n"/>
       <c r="H165" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I165" s="60" t="n">
         <v>17</v>
@@ -13041,7 +12975,7 @@
       <c r="F166" s="58" t="n"/>
       <c r="G166" s="58" t="n"/>
       <c r="H166" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I166" s="60" t="n">
         <v>16</v>
@@ -13074,7 +13008,7 @@
       <c r="F167" s="58" t="n"/>
       <c r="G167" s="58" t="n"/>
       <c r="H167" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I167" s="60" t="n">
         <v>15</v>
@@ -13107,7 +13041,7 @@
       <c r="F168" s="58" t="n"/>
       <c r="G168" s="58" t="n"/>
       <c r="H168" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I168" s="60" t="n">
         <v>14</v>
@@ -13140,7 +13074,7 @@
       <c r="F169" s="58" t="n"/>
       <c r="G169" s="58" t="n"/>
       <c r="H169" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I169" s="60" t="n">
         <v>13</v>
@@ -13173,7 +13107,7 @@
       <c r="F170" s="58" t="n"/>
       <c r="G170" s="58" t="n"/>
       <c r="H170" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I170" s="60" t="n">
         <v>12</v>
@@ -13206,7 +13140,7 @@
       <c r="F171" s="58" t="n"/>
       <c r="G171" s="58" t="n"/>
       <c r="H171" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I171" s="60" t="n">
         <v>11</v>
@@ -13239,7 +13173,7 @@
       <c r="F172" s="58" t="n"/>
       <c r="G172" s="58" t="n"/>
       <c r="H172" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I172" s="60" t="n">
         <v>10</v>
@@ -13272,7 +13206,7 @@
       <c r="F173" s="58" t="n"/>
       <c r="G173" s="58" t="n"/>
       <c r="H173" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I173" s="60" t="n">
         <v>9</v>
@@ -13305,7 +13239,7 @@
       <c r="F174" s="58" t="n"/>
       <c r="G174" s="58" t="n"/>
       <c r="H174" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I174" s="60" t="n">
         <v>8</v>
@@ -13338,7 +13272,7 @@
       <c r="F175" s="58" t="n"/>
       <c r="G175" s="58" t="n"/>
       <c r="H175" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I175" s="60" t="n">
         <v>7</v>
@@ -13371,7 +13305,7 @@
       <c r="F176" s="58" t="n"/>
       <c r="G176" s="58" t="n"/>
       <c r="H176" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I176" s="60" t="n">
         <v>6</v>
@@ -13404,7 +13338,7 @@
       <c r="F177" s="58" t="n"/>
       <c r="G177" s="58" t="n"/>
       <c r="H177" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I177" s="60" t="n">
         <v>5</v>
@@ -13437,7 +13371,7 @@
       <c r="F178" s="58" t="n"/>
       <c r="G178" s="58" t="n"/>
       <c r="H178" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I178" s="60" t="n">
         <v>4</v>
@@ -13470,7 +13404,7 @@
       <c r="F179" s="58" t="n"/>
       <c r="G179" s="58" t="n"/>
       <c r="H179" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I179" s="60" t="n">
         <v>3</v>
@@ -13503,7 +13437,7 @@
       <c r="F180" s="58" t="n"/>
       <c r="G180" s="58" t="n"/>
       <c r="H180" s="60" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I180" s="60" t="n">
         <v>2</v>
@@ -13536,7 +13470,7 @@
       <c r="F181" s="58" t="n"/>
       <c r="G181" s="58" t="n"/>
       <c r="H181" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I181" s="60" t="n">
         <v>17</v>
@@ -13569,7 +13503,7 @@
       <c r="F182" s="58" t="n"/>
       <c r="G182" s="58" t="n"/>
       <c r="H182" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I182" s="60" t="n">
         <v>16</v>
@@ -13602,7 +13536,7 @@
       <c r="F183" s="58" t="n"/>
       <c r="G183" s="58" t="n"/>
       <c r="H183" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I183" s="60" t="n">
         <v>15</v>
@@ -13635,7 +13569,7 @@
       <c r="F184" s="58" t="n"/>
       <c r="G184" s="58" t="n"/>
       <c r="H184" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I184" s="60" t="n">
         <v>14</v>
@@ -13668,7 +13602,7 @@
       <c r="F185" s="58" t="n"/>
       <c r="G185" s="58" t="n"/>
       <c r="H185" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I185" s="60" t="n">
         <v>13</v>
@@ -13701,7 +13635,7 @@
       <c r="F186" s="58" t="n"/>
       <c r="G186" s="58" t="n"/>
       <c r="H186" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I186" s="60" t="n">
         <v>12</v>
@@ -13734,7 +13668,7 @@
       <c r="F187" s="58" t="n"/>
       <c r="G187" s="58" t="n"/>
       <c r="H187" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I187" s="60" t="n">
         <v>11</v>
@@ -13767,7 +13701,7 @@
       <c r="F188" s="58" t="n"/>
       <c r="G188" s="58" t="n"/>
       <c r="H188" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I188" s="60" t="n">
         <v>10</v>
@@ -13800,7 +13734,7 @@
       <c r="F189" s="58" t="n"/>
       <c r="G189" s="58" t="n"/>
       <c r="H189" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I189" s="60" t="n">
         <v>9</v>
@@ -13833,7 +13767,7 @@
       <c r="F190" s="58" t="n"/>
       <c r="G190" s="58" t="n"/>
       <c r="H190" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I190" s="60" t="n">
         <v>8</v>
@@ -13866,7 +13800,7 @@
       <c r="F191" s="58" t="n"/>
       <c r="G191" s="58" t="n"/>
       <c r="H191" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I191" s="60" t="n">
         <v>7</v>
@@ -13899,7 +13833,7 @@
       <c r="F192" s="58" t="n"/>
       <c r="G192" s="58" t="n"/>
       <c r="H192" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I192" s="60" t="n">
         <v>6</v>
@@ -13932,7 +13866,7 @@
       <c r="F193" s="58" t="n"/>
       <c r="G193" s="58" t="n"/>
       <c r="H193" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I193" s="60" t="n">
         <v>5</v>
@@ -13965,7 +13899,7 @@
       <c r="F194" s="58" t="n"/>
       <c r="G194" s="58" t="n"/>
       <c r="H194" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I194" s="60" t="n">
         <v>4</v>
@@ -13998,7 +13932,7 @@
       <c r="F195" s="58" t="n"/>
       <c r="G195" s="58" t="n"/>
       <c r="H195" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I195" s="60" t="n">
         <v>3</v>
@@ -14031,7 +13965,7 @@
       <c r="F196" s="58" t="n"/>
       <c r="G196" s="58" t="n"/>
       <c r="H196" s="60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I196" s="60" t="n">
         <v>2</v>
@@ -14568,12 +14502,12 @@
     <row r="213">
       <c r="A213" s="58" t="inlineStr">
         <is>
-          <t>R1-01-B</t>
+          <t>R2-01-A</t>
         </is>
       </c>
       <c r="B213" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C213" s="61" t="n">
@@ -14581,18 +14515,18 @@
       </c>
       <c r="D213" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E213" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F213" s="58" t="n"/>
       <c r="G213" s="58" t="n"/>
       <c r="H213" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I213" s="60" t="n">
         <v>21</v>
@@ -14601,12 +14535,12 @@
     <row r="214">
       <c r="A214" s="58" t="inlineStr">
         <is>
-          <t>R1-02-B</t>
+          <t>R2-02-A</t>
         </is>
       </c>
       <c r="B214" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C214" s="61" t="n">
@@ -14614,18 +14548,18 @@
       </c>
       <c r="D214" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E214" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F214" s="58" t="n"/>
       <c r="G214" s="58" t="n"/>
       <c r="H214" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I214" s="60" t="n">
         <v>22</v>
@@ -14634,12 +14568,12 @@
     <row r="215">
       <c r="A215" s="58" t="inlineStr">
         <is>
-          <t>R1-03-B</t>
+          <t>R2-03-A</t>
         </is>
       </c>
       <c r="B215" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C215" s="61" t="n">
@@ -14647,18 +14581,18 @@
       </c>
       <c r="D215" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E215" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F215" s="58" t="n"/>
       <c r="G215" s="58" t="n"/>
       <c r="H215" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I215" s="60" t="n">
         <v>23</v>
@@ -14667,12 +14601,12 @@
     <row r="216">
       <c r="A216" s="58" t="inlineStr">
         <is>
-          <t>R1-04-B</t>
+          <t>R2-04-A</t>
         </is>
       </c>
       <c r="B216" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C216" s="61" t="n">
@@ -14680,18 +14614,18 @@
       </c>
       <c r="D216" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E216" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F216" s="58" t="n"/>
       <c r="G216" s="58" t="n"/>
       <c r="H216" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I216" s="60" t="n">
         <v>24</v>
@@ -14700,12 +14634,12 @@
     <row r="217">
       <c r="A217" s="58" t="inlineStr">
         <is>
-          <t>R1-05-B</t>
+          <t>R2-05-A</t>
         </is>
       </c>
       <c r="B217" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C217" s="61" t="n">
@@ -14713,18 +14647,18 @@
       </c>
       <c r="D217" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E217" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F217" s="58" t="n"/>
       <c r="G217" s="58" t="n"/>
       <c r="H217" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I217" s="60" t="n">
         <v>25</v>
@@ -14733,12 +14667,12 @@
     <row r="218">
       <c r="A218" s="58" t="inlineStr">
         <is>
-          <t>R1-06-B</t>
+          <t>R2-06-A</t>
         </is>
       </c>
       <c r="B218" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C218" s="61" t="n">
@@ -14746,18 +14680,18 @@
       </c>
       <c r="D218" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E218" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F218" s="58" t="n"/>
       <c r="G218" s="58" t="n"/>
       <c r="H218" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I218" s="60" t="n">
         <v>26</v>
@@ -14766,12 +14700,12 @@
     <row r="219">
       <c r="A219" s="58" t="inlineStr">
         <is>
-          <t>R1-07-B</t>
+          <t>R2-07-A</t>
         </is>
       </c>
       <c r="B219" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C219" s="61" t="n">
@@ -14779,18 +14713,18 @@
       </c>
       <c r="D219" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E219" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F219" s="58" t="n"/>
       <c r="G219" s="58" t="n"/>
       <c r="H219" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I219" s="60" t="n">
         <v>27</v>
@@ -14799,12 +14733,12 @@
     <row r="220">
       <c r="A220" s="58" t="inlineStr">
         <is>
-          <t>R1-08-B</t>
+          <t>R2-08-A</t>
         </is>
       </c>
       <c r="B220" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C220" s="61" t="n">
@@ -14812,18 +14746,18 @@
       </c>
       <c r="D220" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E220" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F220" s="58" t="n"/>
       <c r="G220" s="58" t="n"/>
       <c r="H220" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I220" s="60" t="n">
         <v>28</v>
@@ -14832,12 +14766,12 @@
     <row r="221">
       <c r="A221" s="58" t="inlineStr">
         <is>
-          <t>R1-09-B</t>
+          <t>R2-09-A</t>
         </is>
       </c>
       <c r="B221" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C221" s="61" t="n">
@@ -14845,18 +14779,18 @@
       </c>
       <c r="D221" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E221" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F221" s="58" t="n"/>
       <c r="G221" s="58" t="n"/>
       <c r="H221" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I221" s="60" t="n">
         <v>29</v>
@@ -14865,12 +14799,12 @@
     <row r="222">
       <c r="A222" s="58" t="inlineStr">
         <is>
-          <t>R1-10-B</t>
+          <t>R2-10-A</t>
         </is>
       </c>
       <c r="B222" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C222" s="61" t="n">
@@ -14878,18 +14812,18 @@
       </c>
       <c r="D222" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E222" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F222" s="58" t="n"/>
       <c r="G222" s="58" t="n"/>
       <c r="H222" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I222" s="60" t="n">
         <v>30</v>
@@ -14898,12 +14832,12 @@
     <row r="223">
       <c r="A223" s="58" t="inlineStr">
         <is>
-          <t>R1-11-B</t>
+          <t>R2-11-A</t>
         </is>
       </c>
       <c r="B223" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C223" s="61" t="n">
@@ -14911,18 +14845,18 @@
       </c>
       <c r="D223" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E223" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F223" s="58" t="n"/>
       <c r="G223" s="58" t="n"/>
       <c r="H223" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I223" s="60" t="n">
         <v>31</v>
@@ -14931,12 +14865,12 @@
     <row r="224">
       <c r="A224" s="58" t="inlineStr">
         <is>
-          <t>R1-12-B</t>
+          <t>R2-12-A</t>
         </is>
       </c>
       <c r="B224" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C224" s="61" t="n">
@@ -14944,18 +14878,18 @@
       </c>
       <c r="D224" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E224" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F224" s="58" t="n"/>
       <c r="G224" s="58" t="n"/>
       <c r="H224" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I224" s="60" t="n">
         <v>32</v>
@@ -14964,12 +14898,12 @@
     <row r="225">
       <c r="A225" s="58" t="inlineStr">
         <is>
-          <t>R1-13-B</t>
+          <t>R2-13-A</t>
         </is>
       </c>
       <c r="B225" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C225" s="61" t="n">
@@ -14977,18 +14911,18 @@
       </c>
       <c r="D225" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E225" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F225" s="58" t="n"/>
       <c r="G225" s="58" t="n"/>
       <c r="H225" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I225" s="60" t="n">
         <v>33</v>
@@ -14997,12 +14931,12 @@
     <row r="226">
       <c r="A226" s="58" t="inlineStr">
         <is>
-          <t>R1-14-B</t>
+          <t>R2-14-A</t>
         </is>
       </c>
       <c r="B226" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C226" s="61" t="n">
@@ -15010,18 +14944,18 @@
       </c>
       <c r="D226" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E226" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F226" s="58" t="n"/>
       <c r="G226" s="58" t="n"/>
       <c r="H226" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I226" s="60" t="n">
         <v>34</v>
@@ -15030,12 +14964,12 @@
     <row r="227">
       <c r="A227" s="58" t="inlineStr">
         <is>
-          <t>R1-15-B</t>
+          <t>R2-15-A</t>
         </is>
       </c>
       <c r="B227" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C227" s="61" t="n">
@@ -15043,18 +14977,18 @@
       </c>
       <c r="D227" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E227" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F227" s="58" t="n"/>
       <c r="G227" s="58" t="n"/>
       <c r="H227" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I227" s="60" t="n">
         <v>35</v>
@@ -15063,12 +14997,12 @@
     <row r="228">
       <c r="A228" s="58" t="inlineStr">
         <is>
-          <t>R1-16-B</t>
+          <t>R2-16-A</t>
         </is>
       </c>
       <c r="B228" s="60" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="C228" s="61" t="n">
@@ -15076,18 +15010,18 @@
       </c>
       <c r="D228" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E228" s="60" t="inlineStr">
         <is>
-          <t>LBL</t>
+          <t>FLM</t>
         </is>
       </c>
       <c r="F228" s="58" t="n"/>
       <c r="G228" s="58" t="n"/>
       <c r="H228" s="60" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I228" s="60" t="n">
         <v>36</v>
@@ -15096,7 +15030,7 @@
     <row r="229">
       <c r="A229" s="58" t="inlineStr">
         <is>
-          <t>R2-01-A</t>
+          <t>R2-01-B</t>
         </is>
       </c>
       <c r="B229" s="60" t="inlineStr">
@@ -15109,7 +15043,7 @@
       </c>
       <c r="D229" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E229" s="60" t="inlineStr">
@@ -15120,7 +15054,7 @@
       <c r="F229" s="58" t="n"/>
       <c r="G229" s="58" t="n"/>
       <c r="H229" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I229" s="60" t="n">
         <v>21</v>
@@ -15129,7 +15063,7 @@
     <row r="230">
       <c r="A230" s="58" t="inlineStr">
         <is>
-          <t>R2-02-A</t>
+          <t>R2-02-B</t>
         </is>
       </c>
       <c r="B230" s="60" t="inlineStr">
@@ -15142,7 +15076,7 @@
       </c>
       <c r="D230" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E230" s="60" t="inlineStr">
@@ -15153,7 +15087,7 @@
       <c r="F230" s="58" t="n"/>
       <c r="G230" s="58" t="n"/>
       <c r="H230" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I230" s="60" t="n">
         <v>22</v>
@@ -15162,7 +15096,7 @@
     <row r="231">
       <c r="A231" s="58" t="inlineStr">
         <is>
-          <t>R2-03-A</t>
+          <t>R2-03-B</t>
         </is>
       </c>
       <c r="B231" s="60" t="inlineStr">
@@ -15175,7 +15109,7 @@
       </c>
       <c r="D231" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E231" s="60" t="inlineStr">
@@ -15186,7 +15120,7 @@
       <c r="F231" s="58" t="n"/>
       <c r="G231" s="58" t="n"/>
       <c r="H231" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I231" s="60" t="n">
         <v>23</v>
@@ -15195,7 +15129,7 @@
     <row r="232">
       <c r="A232" s="58" t="inlineStr">
         <is>
-          <t>R2-04-A</t>
+          <t>R2-04-B</t>
         </is>
       </c>
       <c r="B232" s="60" t="inlineStr">
@@ -15208,7 +15142,7 @@
       </c>
       <c r="D232" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E232" s="60" t="inlineStr">
@@ -15219,7 +15153,7 @@
       <c r="F232" s="58" t="n"/>
       <c r="G232" s="58" t="n"/>
       <c r="H232" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I232" s="60" t="n">
         <v>24</v>
@@ -15228,7 +15162,7 @@
     <row r="233">
       <c r="A233" s="58" t="inlineStr">
         <is>
-          <t>R2-05-A</t>
+          <t>R2-05-B</t>
         </is>
       </c>
       <c r="B233" s="60" t="inlineStr">
@@ -15241,7 +15175,7 @@
       </c>
       <c r="D233" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E233" s="60" t="inlineStr">
@@ -15252,7 +15186,7 @@
       <c r="F233" s="58" t="n"/>
       <c r="G233" s="58" t="n"/>
       <c r="H233" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I233" s="60" t="n">
         <v>25</v>
@@ -15261,7 +15195,7 @@
     <row r="234">
       <c r="A234" s="58" t="inlineStr">
         <is>
-          <t>R2-06-A</t>
+          <t>R2-06-B</t>
         </is>
       </c>
       <c r="B234" s="60" t="inlineStr">
@@ -15274,7 +15208,7 @@
       </c>
       <c r="D234" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E234" s="60" t="inlineStr">
@@ -15285,7 +15219,7 @@
       <c r="F234" s="58" t="n"/>
       <c r="G234" s="58" t="n"/>
       <c r="H234" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I234" s="60" t="n">
         <v>26</v>
@@ -15294,7 +15228,7 @@
     <row r="235">
       <c r="A235" s="58" t="inlineStr">
         <is>
-          <t>R2-07-A</t>
+          <t>R2-07-B</t>
         </is>
       </c>
       <c r="B235" s="60" t="inlineStr">
@@ -15307,7 +15241,7 @@
       </c>
       <c r="D235" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E235" s="60" t="inlineStr">
@@ -15318,7 +15252,7 @@
       <c r="F235" s="58" t="n"/>
       <c r="G235" s="58" t="n"/>
       <c r="H235" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I235" s="60" t="n">
         <v>27</v>
@@ -15327,7 +15261,7 @@
     <row r="236">
       <c r="A236" s="58" t="inlineStr">
         <is>
-          <t>R2-08-A</t>
+          <t>R2-08-B</t>
         </is>
       </c>
       <c r="B236" s="60" t="inlineStr">
@@ -15340,7 +15274,7 @@
       </c>
       <c r="D236" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E236" s="60" t="inlineStr">
@@ -15351,7 +15285,7 @@
       <c r="F236" s="58" t="n"/>
       <c r="G236" s="58" t="n"/>
       <c r="H236" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I236" s="60" t="n">
         <v>28</v>
@@ -15360,7 +15294,7 @@
     <row r="237">
       <c r="A237" s="58" t="inlineStr">
         <is>
-          <t>R2-09-A</t>
+          <t>R2-09-B</t>
         </is>
       </c>
       <c r="B237" s="60" t="inlineStr">
@@ -15373,7 +15307,7 @@
       </c>
       <c r="D237" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E237" s="60" t="inlineStr">
@@ -15384,7 +15318,7 @@
       <c r="F237" s="58" t="n"/>
       <c r="G237" s="58" t="n"/>
       <c r="H237" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I237" s="60" t="n">
         <v>29</v>
@@ -15393,7 +15327,7 @@
     <row r="238">
       <c r="A238" s="58" t="inlineStr">
         <is>
-          <t>R2-10-A</t>
+          <t>R2-10-B</t>
         </is>
       </c>
       <c r="B238" s="60" t="inlineStr">
@@ -15406,7 +15340,7 @@
       </c>
       <c r="D238" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E238" s="60" t="inlineStr">
@@ -15417,7 +15351,7 @@
       <c r="F238" s="58" t="n"/>
       <c r="G238" s="58" t="n"/>
       <c r="H238" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I238" s="60" t="n">
         <v>30</v>
@@ -15426,7 +15360,7 @@
     <row r="239">
       <c r="A239" s="58" t="inlineStr">
         <is>
-          <t>R2-11-A</t>
+          <t>R2-11-B</t>
         </is>
       </c>
       <c r="B239" s="60" t="inlineStr">
@@ -15439,7 +15373,7 @@
       </c>
       <c r="D239" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E239" s="60" t="inlineStr">
@@ -15450,7 +15384,7 @@
       <c r="F239" s="58" t="n"/>
       <c r="G239" s="58" t="n"/>
       <c r="H239" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I239" s="60" t="n">
         <v>31</v>
@@ -15459,7 +15393,7 @@
     <row r="240">
       <c r="A240" s="58" t="inlineStr">
         <is>
-          <t>R2-12-A</t>
+          <t>R2-12-B</t>
         </is>
       </c>
       <c r="B240" s="60" t="inlineStr">
@@ -15472,7 +15406,7 @@
       </c>
       <c r="D240" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E240" s="60" t="inlineStr">
@@ -15483,7 +15417,7 @@
       <c r="F240" s="58" t="n"/>
       <c r="G240" s="58" t="n"/>
       <c r="H240" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I240" s="60" t="n">
         <v>32</v>
@@ -15492,7 +15426,7 @@
     <row r="241">
       <c r="A241" s="58" t="inlineStr">
         <is>
-          <t>R2-13-A</t>
+          <t>R2-13-B</t>
         </is>
       </c>
       <c r="B241" s="60" t="inlineStr">
@@ -15505,7 +15439,7 @@
       </c>
       <c r="D241" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E241" s="60" t="inlineStr">
@@ -15516,7 +15450,7 @@
       <c r="F241" s="58" t="n"/>
       <c r="G241" s="58" t="n"/>
       <c r="H241" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I241" s="60" t="n">
         <v>33</v>
@@ -15525,7 +15459,7 @@
     <row r="242">
       <c r="A242" s="58" t="inlineStr">
         <is>
-          <t>R2-14-A</t>
+          <t>R2-14-B</t>
         </is>
       </c>
       <c r="B242" s="60" t="inlineStr">
@@ -15538,7 +15472,7 @@
       </c>
       <c r="D242" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E242" s="60" t="inlineStr">
@@ -15549,7 +15483,7 @@
       <c r="F242" s="58" t="n"/>
       <c r="G242" s="58" t="n"/>
       <c r="H242" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I242" s="60" t="n">
         <v>34</v>
@@ -15558,7 +15492,7 @@
     <row r="243">
       <c r="A243" s="58" t="inlineStr">
         <is>
-          <t>R2-15-A</t>
+          <t>R2-15-B</t>
         </is>
       </c>
       <c r="B243" s="60" t="inlineStr">
@@ -15571,7 +15505,7 @@
       </c>
       <c r="D243" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E243" s="60" t="inlineStr">
@@ -15582,7 +15516,7 @@
       <c r="F243" s="58" t="n"/>
       <c r="G243" s="58" t="n"/>
       <c r="H243" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I243" s="60" t="n">
         <v>35</v>
@@ -15591,7 +15525,7 @@
     <row r="244">
       <c r="A244" s="58" t="inlineStr">
         <is>
-          <t>R2-16-A</t>
+          <t>R2-16-B</t>
         </is>
       </c>
       <c r="B244" s="60" t="inlineStr">
@@ -15604,7 +15538,7 @@
       </c>
       <c r="D244" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E244" s="60" t="inlineStr">
@@ -15615,7 +15549,7 @@
       <c r="F244" s="58" t="n"/>
       <c r="G244" s="58" t="n"/>
       <c r="H244" s="60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I244" s="60" t="n">
         <v>36</v>
@@ -15624,7 +15558,7 @@
     <row r="245">
       <c r="A245" s="58" t="inlineStr">
         <is>
-          <t>R2-01-B</t>
+          <t>R2-01-C</t>
         </is>
       </c>
       <c r="B245" s="60" t="inlineStr">
@@ -15637,7 +15571,7 @@
       </c>
       <c r="D245" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E245" s="60" t="inlineStr">
@@ -15648,7 +15582,7 @@
       <c r="F245" s="58" t="n"/>
       <c r="G245" s="58" t="n"/>
       <c r="H245" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I245" s="60" t="n">
         <v>21</v>
@@ -15657,7 +15591,7 @@
     <row r="246">
       <c r="A246" s="58" t="inlineStr">
         <is>
-          <t>R2-02-B</t>
+          <t>R2-02-C</t>
         </is>
       </c>
       <c r="B246" s="60" t="inlineStr">
@@ -15670,7 +15604,7 @@
       </c>
       <c r="D246" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E246" s="60" t="inlineStr">
@@ -15681,7 +15615,7 @@
       <c r="F246" s="58" t="n"/>
       <c r="G246" s="58" t="n"/>
       <c r="H246" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I246" s="60" t="n">
         <v>22</v>
@@ -15690,7 +15624,7 @@
     <row r="247">
       <c r="A247" s="58" t="inlineStr">
         <is>
-          <t>R2-03-B</t>
+          <t>R2-03-C</t>
         </is>
       </c>
       <c r="B247" s="60" t="inlineStr">
@@ -15703,7 +15637,7 @@
       </c>
       <c r="D247" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E247" s="60" t="inlineStr">
@@ -15714,7 +15648,7 @@
       <c r="F247" s="58" t="n"/>
       <c r="G247" s="58" t="n"/>
       <c r="H247" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I247" s="60" t="n">
         <v>23</v>
@@ -15723,7 +15657,7 @@
     <row r="248">
       <c r="A248" s="58" t="inlineStr">
         <is>
-          <t>R2-04-B</t>
+          <t>R2-04-C</t>
         </is>
       </c>
       <c r="B248" s="60" t="inlineStr">
@@ -15736,7 +15670,7 @@
       </c>
       <c r="D248" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E248" s="60" t="inlineStr">
@@ -15747,7 +15681,7 @@
       <c r="F248" s="58" t="n"/>
       <c r="G248" s="58" t="n"/>
       <c r="H248" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I248" s="60" t="n">
         <v>24</v>
@@ -15756,7 +15690,7 @@
     <row r="249">
       <c r="A249" s="58" t="inlineStr">
         <is>
-          <t>R2-05-B</t>
+          <t>R2-05-C</t>
         </is>
       </c>
       <c r="B249" s="60" t="inlineStr">
@@ -15769,7 +15703,7 @@
       </c>
       <c r="D249" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E249" s="60" t="inlineStr">
@@ -15780,7 +15714,7 @@
       <c r="F249" s="58" t="n"/>
       <c r="G249" s="58" t="n"/>
       <c r="H249" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I249" s="60" t="n">
         <v>25</v>
@@ -15789,7 +15723,7 @@
     <row r="250">
       <c r="A250" s="58" t="inlineStr">
         <is>
-          <t>R2-06-B</t>
+          <t>R2-06-C</t>
         </is>
       </c>
       <c r="B250" s="60" t="inlineStr">
@@ -15802,7 +15736,7 @@
       </c>
       <c r="D250" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E250" s="60" t="inlineStr">
@@ -15813,7 +15747,7 @@
       <c r="F250" s="58" t="n"/>
       <c r="G250" s="58" t="n"/>
       <c r="H250" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I250" s="60" t="n">
         <v>26</v>
@@ -15822,7 +15756,7 @@
     <row r="251">
       <c r="A251" s="58" t="inlineStr">
         <is>
-          <t>R2-07-B</t>
+          <t>R2-07-C</t>
         </is>
       </c>
       <c r="B251" s="60" t="inlineStr">
@@ -15835,7 +15769,7 @@
       </c>
       <c r="D251" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E251" s="60" t="inlineStr">
@@ -15846,7 +15780,7 @@
       <c r="F251" s="58" t="n"/>
       <c r="G251" s="58" t="n"/>
       <c r="H251" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I251" s="60" t="n">
         <v>27</v>
@@ -15855,7 +15789,7 @@
     <row r="252">
       <c r="A252" s="58" t="inlineStr">
         <is>
-          <t>R2-08-B</t>
+          <t>R2-08-C</t>
         </is>
       </c>
       <c r="B252" s="60" t="inlineStr">
@@ -15868,7 +15802,7 @@
       </c>
       <c r="D252" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E252" s="60" t="inlineStr">
@@ -15879,7 +15813,7 @@
       <c r="F252" s="58" t="n"/>
       <c r="G252" s="58" t="n"/>
       <c r="H252" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I252" s="60" t="n">
         <v>28</v>
@@ -15888,7 +15822,7 @@
     <row r="253">
       <c r="A253" s="58" t="inlineStr">
         <is>
-          <t>R2-09-B</t>
+          <t>R2-09-C</t>
         </is>
       </c>
       <c r="B253" s="60" t="inlineStr">
@@ -15901,7 +15835,7 @@
       </c>
       <c r="D253" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E253" s="60" t="inlineStr">
@@ -15912,7 +15846,7 @@
       <c r="F253" s="58" t="n"/>
       <c r="G253" s="58" t="n"/>
       <c r="H253" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I253" s="60" t="n">
         <v>29</v>
@@ -15921,7 +15855,7 @@
     <row r="254">
       <c r="A254" s="58" t="inlineStr">
         <is>
-          <t>R2-10-B</t>
+          <t>R2-10-C</t>
         </is>
       </c>
       <c r="B254" s="60" t="inlineStr">
@@ -15934,7 +15868,7 @@
       </c>
       <c r="D254" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E254" s="60" t="inlineStr">
@@ -15945,7 +15879,7 @@
       <c r="F254" s="58" t="n"/>
       <c r="G254" s="58" t="n"/>
       <c r="H254" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I254" s="60" t="n">
         <v>30</v>
@@ -15954,7 +15888,7 @@
     <row r="255">
       <c r="A255" s="58" t="inlineStr">
         <is>
-          <t>R2-11-B</t>
+          <t>R2-11-C</t>
         </is>
       </c>
       <c r="B255" s="60" t="inlineStr">
@@ -15967,7 +15901,7 @@
       </c>
       <c r="D255" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E255" s="60" t="inlineStr">
@@ -15978,7 +15912,7 @@
       <c r="F255" s="58" t="n"/>
       <c r="G255" s="58" t="n"/>
       <c r="H255" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I255" s="60" t="n">
         <v>31</v>
@@ -15987,7 +15921,7 @@
     <row r="256">
       <c r="A256" s="58" t="inlineStr">
         <is>
-          <t>R2-12-B</t>
+          <t>R2-12-C</t>
         </is>
       </c>
       <c r="B256" s="60" t="inlineStr">
@@ -16000,7 +15934,7 @@
       </c>
       <c r="D256" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E256" s="60" t="inlineStr">
@@ -16011,7 +15945,7 @@
       <c r="F256" s="58" t="n"/>
       <c r="G256" s="58" t="n"/>
       <c r="H256" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I256" s="60" t="n">
         <v>32</v>
@@ -16020,7 +15954,7 @@
     <row r="257">
       <c r="A257" s="58" t="inlineStr">
         <is>
-          <t>R2-13-B</t>
+          <t>R2-13-C</t>
         </is>
       </c>
       <c r="B257" s="60" t="inlineStr">
@@ -16033,7 +15967,7 @@
       </c>
       <c r="D257" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E257" s="60" t="inlineStr">
@@ -16044,7 +15978,7 @@
       <c r="F257" s="58" t="n"/>
       <c r="G257" s="58" t="n"/>
       <c r="H257" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I257" s="60" t="n">
         <v>33</v>
@@ -16053,7 +15987,7 @@
     <row r="258">
       <c r="A258" s="58" t="inlineStr">
         <is>
-          <t>R2-14-B</t>
+          <t>R2-14-C</t>
         </is>
       </c>
       <c r="B258" s="60" t="inlineStr">
@@ -16066,7 +16000,7 @@
       </c>
       <c r="D258" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E258" s="60" t="inlineStr">
@@ -16077,7 +16011,7 @@
       <c r="F258" s="58" t="n"/>
       <c r="G258" s="58" t="n"/>
       <c r="H258" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I258" s="60" t="n">
         <v>34</v>
@@ -16086,7 +16020,7 @@
     <row r="259">
       <c r="A259" s="58" t="inlineStr">
         <is>
-          <t>R2-15-B</t>
+          <t>R2-15-C</t>
         </is>
       </c>
       <c r="B259" s="60" t="inlineStr">
@@ -16099,7 +16033,7 @@
       </c>
       <c r="D259" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E259" s="60" t="inlineStr">
@@ -16110,7 +16044,7 @@
       <c r="F259" s="58" t="n"/>
       <c r="G259" s="58" t="n"/>
       <c r="H259" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I259" s="60" t="n">
         <v>35</v>
@@ -16119,7 +16053,7 @@
     <row r="260">
       <c r="A260" s="58" t="inlineStr">
         <is>
-          <t>R2-16-B</t>
+          <t>R2-16-C</t>
         </is>
       </c>
       <c r="B260" s="60" t="inlineStr">
@@ -16132,7 +16066,7 @@
       </c>
       <c r="D260" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E260" s="60" t="inlineStr">
@@ -16143,7 +16077,7 @@
       <c r="F260" s="58" t="n"/>
       <c r="G260" s="58" t="n"/>
       <c r="H260" s="60" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I260" s="60" t="n">
         <v>36</v>
@@ -16152,7 +16086,7 @@
     <row r="261">
       <c r="A261" s="58" t="inlineStr">
         <is>
-          <t>R2-01-C</t>
+          <t>R2-01-D</t>
         </is>
       </c>
       <c r="B261" s="60" t="inlineStr">
@@ -16165,7 +16099,7 @@
       </c>
       <c r="D261" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E261" s="60" t="inlineStr">
@@ -16176,7 +16110,7 @@
       <c r="F261" s="58" t="n"/>
       <c r="G261" s="58" t="n"/>
       <c r="H261" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I261" s="60" t="n">
         <v>21</v>
@@ -16185,7 +16119,7 @@
     <row r="262">
       <c r="A262" s="58" t="inlineStr">
         <is>
-          <t>R2-02-C</t>
+          <t>R2-02-D</t>
         </is>
       </c>
       <c r="B262" s="60" t="inlineStr">
@@ -16198,7 +16132,7 @@
       </c>
       <c r="D262" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E262" s="60" t="inlineStr">
@@ -16209,7 +16143,7 @@
       <c r="F262" s="58" t="n"/>
       <c r="G262" s="58" t="n"/>
       <c r="H262" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I262" s="60" t="n">
         <v>22</v>
@@ -16218,7 +16152,7 @@
     <row r="263">
       <c r="A263" s="58" t="inlineStr">
         <is>
-          <t>R2-03-C</t>
+          <t>R2-03-D</t>
         </is>
       </c>
       <c r="B263" s="60" t="inlineStr">
@@ -16231,7 +16165,7 @@
       </c>
       <c r="D263" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E263" s="60" t="inlineStr">
@@ -16242,7 +16176,7 @@
       <c r="F263" s="58" t="n"/>
       <c r="G263" s="58" t="n"/>
       <c r="H263" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I263" s="60" t="n">
         <v>23</v>
@@ -16251,7 +16185,7 @@
     <row r="264">
       <c r="A264" s="58" t="inlineStr">
         <is>
-          <t>R2-04-C</t>
+          <t>R2-04-D</t>
         </is>
       </c>
       <c r="B264" s="60" t="inlineStr">
@@ -16264,7 +16198,7 @@
       </c>
       <c r="D264" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E264" s="60" t="inlineStr">
@@ -16275,7 +16209,7 @@
       <c r="F264" s="58" t="n"/>
       <c r="G264" s="58" t="n"/>
       <c r="H264" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I264" s="60" t="n">
         <v>24</v>
@@ -16284,7 +16218,7 @@
     <row r="265">
       <c r="A265" s="58" t="inlineStr">
         <is>
-          <t>R2-05-C</t>
+          <t>R2-05-D</t>
         </is>
       </c>
       <c r="B265" s="60" t="inlineStr">
@@ -16297,7 +16231,7 @@
       </c>
       <c r="D265" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E265" s="60" t="inlineStr">
@@ -16308,7 +16242,7 @@
       <c r="F265" s="58" t="n"/>
       <c r="G265" s="58" t="n"/>
       <c r="H265" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I265" s="60" t="n">
         <v>25</v>
@@ -16317,7 +16251,7 @@
     <row r="266">
       <c r="A266" s="58" t="inlineStr">
         <is>
-          <t>R2-06-C</t>
+          <t>R2-06-D</t>
         </is>
       </c>
       <c r="B266" s="60" t="inlineStr">
@@ -16330,7 +16264,7 @@
       </c>
       <c r="D266" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E266" s="60" t="inlineStr">
@@ -16341,7 +16275,7 @@
       <c r="F266" s="58" t="n"/>
       <c r="G266" s="58" t="n"/>
       <c r="H266" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I266" s="60" t="n">
         <v>26</v>
@@ -16350,7 +16284,7 @@
     <row r="267">
       <c r="A267" s="58" t="inlineStr">
         <is>
-          <t>R2-07-C</t>
+          <t>R2-07-D</t>
         </is>
       </c>
       <c r="B267" s="60" t="inlineStr">
@@ -16363,7 +16297,7 @@
       </c>
       <c r="D267" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E267" s="60" t="inlineStr">
@@ -16374,7 +16308,7 @@
       <c r="F267" s="58" t="n"/>
       <c r="G267" s="58" t="n"/>
       <c r="H267" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I267" s="60" t="n">
         <v>27</v>
@@ -16383,7 +16317,7 @@
     <row r="268">
       <c r="A268" s="58" t="inlineStr">
         <is>
-          <t>R2-08-C</t>
+          <t>R2-08-D</t>
         </is>
       </c>
       <c r="B268" s="60" t="inlineStr">
@@ -16396,7 +16330,7 @@
       </c>
       <c r="D268" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E268" s="60" t="inlineStr">
@@ -16407,7 +16341,7 @@
       <c r="F268" s="58" t="n"/>
       <c r="G268" s="58" t="n"/>
       <c r="H268" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I268" s="60" t="n">
         <v>28</v>
@@ -16416,7 +16350,7 @@
     <row r="269">
       <c r="A269" s="58" t="inlineStr">
         <is>
-          <t>R2-09-C</t>
+          <t>R2-09-D</t>
         </is>
       </c>
       <c r="B269" s="60" t="inlineStr">
@@ -16429,7 +16363,7 @@
       </c>
       <c r="D269" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E269" s="60" t="inlineStr">
@@ -16440,7 +16374,7 @@
       <c r="F269" s="58" t="n"/>
       <c r="G269" s="58" t="n"/>
       <c r="H269" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I269" s="60" t="n">
         <v>29</v>
@@ -16449,7 +16383,7 @@
     <row r="270">
       <c r="A270" s="58" t="inlineStr">
         <is>
-          <t>R2-10-C</t>
+          <t>R2-10-D</t>
         </is>
       </c>
       <c r="B270" s="60" t="inlineStr">
@@ -16462,7 +16396,7 @@
       </c>
       <c r="D270" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E270" s="60" t="inlineStr">
@@ -16473,7 +16407,7 @@
       <c r="F270" s="58" t="n"/>
       <c r="G270" s="58" t="n"/>
       <c r="H270" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I270" s="60" t="n">
         <v>30</v>
@@ -16482,7 +16416,7 @@
     <row r="271">
       <c r="A271" s="58" t="inlineStr">
         <is>
-          <t>R2-11-C</t>
+          <t>R2-11-D</t>
         </is>
       </c>
       <c r="B271" s="60" t="inlineStr">
@@ -16495,7 +16429,7 @@
       </c>
       <c r="D271" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E271" s="60" t="inlineStr">
@@ -16506,7 +16440,7 @@
       <c r="F271" s="58" t="n"/>
       <c r="G271" s="58" t="n"/>
       <c r="H271" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I271" s="60" t="n">
         <v>31</v>
@@ -16515,7 +16449,7 @@
     <row r="272">
       <c r="A272" s="58" t="inlineStr">
         <is>
-          <t>R2-12-C</t>
+          <t>R2-12-D</t>
         </is>
       </c>
       <c r="B272" s="60" t="inlineStr">
@@ -16528,7 +16462,7 @@
       </c>
       <c r="D272" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E272" s="60" t="inlineStr">
@@ -16539,7 +16473,7 @@
       <c r="F272" s="58" t="n"/>
       <c r="G272" s="58" t="n"/>
       <c r="H272" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I272" s="60" t="n">
         <v>32</v>
@@ -16548,7 +16482,7 @@
     <row r="273">
       <c r="A273" s="58" t="inlineStr">
         <is>
-          <t>R2-13-C</t>
+          <t>R2-13-D</t>
         </is>
       </c>
       <c r="B273" s="60" t="inlineStr">
@@ -16561,7 +16495,7 @@
       </c>
       <c r="D273" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E273" s="60" t="inlineStr">
@@ -16572,7 +16506,7 @@
       <c r="F273" s="58" t="n"/>
       <c r="G273" s="58" t="n"/>
       <c r="H273" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I273" s="60" t="n">
         <v>33</v>
@@ -16581,7 +16515,7 @@
     <row r="274">
       <c r="A274" s="58" t="inlineStr">
         <is>
-          <t>R2-14-C</t>
+          <t>R2-14-D</t>
         </is>
       </c>
       <c r="B274" s="60" t="inlineStr">
@@ -16594,7 +16528,7 @@
       </c>
       <c r="D274" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E274" s="60" t="inlineStr">
@@ -16605,7 +16539,7 @@
       <c r="F274" s="58" t="n"/>
       <c r="G274" s="58" t="n"/>
       <c r="H274" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I274" s="60" t="n">
         <v>34</v>
@@ -16614,7 +16548,7 @@
     <row r="275">
       <c r="A275" s="58" t="inlineStr">
         <is>
-          <t>R2-15-C</t>
+          <t>R2-15-D</t>
         </is>
       </c>
       <c r="B275" s="60" t="inlineStr">
@@ -16627,7 +16561,7 @@
       </c>
       <c r="D275" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E275" s="60" t="inlineStr">
@@ -16638,7 +16572,7 @@
       <c r="F275" s="58" t="n"/>
       <c r="G275" s="58" t="n"/>
       <c r="H275" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I275" s="60" t="n">
         <v>35</v>
@@ -16647,7 +16581,7 @@
     <row r="276">
       <c r="A276" s="58" t="inlineStr">
         <is>
-          <t>R2-16-C</t>
+          <t>R2-16-D</t>
         </is>
       </c>
       <c r="B276" s="60" t="inlineStr">
@@ -16660,7 +16594,7 @@
       </c>
       <c r="D276" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E276" s="60" t="inlineStr">
@@ -16671,7 +16605,7 @@
       <c r="F276" s="58" t="n"/>
       <c r="G276" s="58" t="n"/>
       <c r="H276" s="60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I276" s="60" t="n">
         <v>36</v>
@@ -16680,12 +16614,12 @@
     <row r="277">
       <c r="A277" s="58" t="inlineStr">
         <is>
-          <t>R2-01-D</t>
+          <t>R3-01-A</t>
         </is>
       </c>
       <c r="B277" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C277" s="61" t="n">
@@ -16693,18 +16627,18 @@
       </c>
       <c r="D277" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E277" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F277" s="58" t="n"/>
       <c r="G277" s="58" t="n"/>
       <c r="H277" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I277" s="60" t="n">
         <v>21</v>
@@ -16713,12 +16647,12 @@
     <row r="278">
       <c r="A278" s="58" t="inlineStr">
         <is>
-          <t>R2-02-D</t>
+          <t>R3-02-A</t>
         </is>
       </c>
       <c r="B278" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C278" s="61" t="n">
@@ -16726,18 +16660,18 @@
       </c>
       <c r="D278" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E278" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F278" s="58" t="n"/>
       <c r="G278" s="58" t="n"/>
       <c r="H278" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I278" s="60" t="n">
         <v>22</v>
@@ -16746,12 +16680,12 @@
     <row r="279">
       <c r="A279" s="58" t="inlineStr">
         <is>
-          <t>R2-03-D</t>
+          <t>R3-03-A</t>
         </is>
       </c>
       <c r="B279" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C279" s="61" t="n">
@@ -16759,18 +16693,18 @@
       </c>
       <c r="D279" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E279" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F279" s="58" t="n"/>
       <c r="G279" s="58" t="n"/>
       <c r="H279" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I279" s="60" t="n">
         <v>23</v>
@@ -16779,12 +16713,12 @@
     <row r="280">
       <c r="A280" s="58" t="inlineStr">
         <is>
-          <t>R2-04-D</t>
+          <t>R3-04-A</t>
         </is>
       </c>
       <c r="B280" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C280" s="61" t="n">
@@ -16792,18 +16726,18 @@
       </c>
       <c r="D280" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E280" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F280" s="58" t="n"/>
       <c r="G280" s="58" t="n"/>
       <c r="H280" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I280" s="60" t="n">
         <v>24</v>
@@ -16812,12 +16746,12 @@
     <row r="281">
       <c r="A281" s="58" t="inlineStr">
         <is>
-          <t>R2-05-D</t>
+          <t>R3-05-A</t>
         </is>
       </c>
       <c r="B281" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C281" s="61" t="n">
@@ -16825,18 +16759,18 @@
       </c>
       <c r="D281" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E281" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F281" s="58" t="n"/>
       <c r="G281" s="58" t="n"/>
       <c r="H281" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I281" s="60" t="n">
         <v>25</v>
@@ -16845,12 +16779,12 @@
     <row r="282">
       <c r="A282" s="58" t="inlineStr">
         <is>
-          <t>R2-06-D</t>
+          <t>R3-06-A</t>
         </is>
       </c>
       <c r="B282" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C282" s="61" t="n">
@@ -16858,18 +16792,18 @@
       </c>
       <c r="D282" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E282" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F282" s="58" t="n"/>
       <c r="G282" s="58" t="n"/>
       <c r="H282" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I282" s="60" t="n">
         <v>26</v>
@@ -16878,12 +16812,12 @@
     <row r="283">
       <c r="A283" s="58" t="inlineStr">
         <is>
-          <t>R2-07-D</t>
+          <t>R3-07-A</t>
         </is>
       </c>
       <c r="B283" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C283" s="61" t="n">
@@ -16891,18 +16825,18 @@
       </c>
       <c r="D283" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E283" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F283" s="58" t="n"/>
       <c r="G283" s="58" t="n"/>
       <c r="H283" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I283" s="60" t="n">
         <v>27</v>
@@ -16911,12 +16845,12 @@
     <row r="284">
       <c r="A284" s="58" t="inlineStr">
         <is>
-          <t>R2-08-D</t>
+          <t>R3-08-A</t>
         </is>
       </c>
       <c r="B284" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C284" s="61" t="n">
@@ -16924,18 +16858,18 @@
       </c>
       <c r="D284" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E284" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F284" s="58" t="n"/>
       <c r="G284" s="58" t="n"/>
       <c r="H284" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I284" s="60" t="n">
         <v>28</v>
@@ -16944,12 +16878,12 @@
     <row r="285">
       <c r="A285" s="58" t="inlineStr">
         <is>
-          <t>R2-09-D</t>
+          <t>R3-09-A</t>
         </is>
       </c>
       <c r="B285" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C285" s="61" t="n">
@@ -16957,18 +16891,18 @@
       </c>
       <c r="D285" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E285" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F285" s="58" t="n"/>
       <c r="G285" s="58" t="n"/>
       <c r="H285" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I285" s="60" t="n">
         <v>29</v>
@@ -16977,12 +16911,12 @@
     <row r="286">
       <c r="A286" s="58" t="inlineStr">
         <is>
-          <t>R2-10-D</t>
+          <t>R3-10-A</t>
         </is>
       </c>
       <c r="B286" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C286" s="61" t="n">
@@ -16990,18 +16924,18 @@
       </c>
       <c r="D286" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E286" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F286" s="58" t="n"/>
       <c r="G286" s="58" t="n"/>
       <c r="H286" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I286" s="60" t="n">
         <v>30</v>
@@ -17010,12 +16944,12 @@
     <row r="287">
       <c r="A287" s="58" t="inlineStr">
         <is>
-          <t>R2-11-D</t>
+          <t>R3-11-A</t>
         </is>
       </c>
       <c r="B287" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C287" s="61" t="n">
@@ -17023,18 +16957,18 @@
       </c>
       <c r="D287" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E287" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F287" s="58" t="n"/>
       <c r="G287" s="58" t="n"/>
       <c r="H287" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I287" s="60" t="n">
         <v>31</v>
@@ -17043,12 +16977,12 @@
     <row r="288">
       <c r="A288" s="58" t="inlineStr">
         <is>
-          <t>R2-12-D</t>
+          <t>R3-12-A</t>
         </is>
       </c>
       <c r="B288" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C288" s="61" t="n">
@@ -17056,18 +16990,18 @@
       </c>
       <c r="D288" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E288" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F288" s="58" t="n"/>
       <c r="G288" s="58" t="n"/>
       <c r="H288" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I288" s="60" t="n">
         <v>32</v>
@@ -17076,12 +17010,12 @@
     <row r="289">
       <c r="A289" s="58" t="inlineStr">
         <is>
-          <t>R2-13-D</t>
+          <t>R3-13-A</t>
         </is>
       </c>
       <c r="B289" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C289" s="61" t="n">
@@ -17089,18 +17023,18 @@
       </c>
       <c r="D289" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E289" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F289" s="58" t="n"/>
       <c r="G289" s="58" t="n"/>
       <c r="H289" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I289" s="60" t="n">
         <v>33</v>
@@ -17109,12 +17043,12 @@
     <row r="290">
       <c r="A290" s="58" t="inlineStr">
         <is>
-          <t>R2-14-D</t>
+          <t>R3-14-A</t>
         </is>
       </c>
       <c r="B290" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C290" s="61" t="n">
@@ -17122,18 +17056,18 @@
       </c>
       <c r="D290" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E290" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F290" s="58" t="n"/>
       <c r="G290" s="58" t="n"/>
       <c r="H290" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I290" s="60" t="n">
         <v>34</v>
@@ -17142,12 +17076,12 @@
     <row r="291">
       <c r="A291" s="58" t="inlineStr">
         <is>
-          <t>R2-15-D</t>
+          <t>R3-15-A</t>
         </is>
       </c>
       <c r="B291" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C291" s="61" t="n">
@@ -17155,18 +17089,18 @@
       </c>
       <c r="D291" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E291" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F291" s="58" t="n"/>
       <c r="G291" s="58" t="n"/>
       <c r="H291" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I291" s="60" t="n">
         <v>35</v>
@@ -17175,12 +17109,12 @@
     <row r="292">
       <c r="A292" s="58" t="inlineStr">
         <is>
-          <t>R2-16-D</t>
+          <t>R3-16-A</t>
         </is>
       </c>
       <c r="B292" s="60" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="C292" s="61" t="n">
@@ -17188,18 +17122,18 @@
       </c>
       <c r="D292" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E292" s="60" t="inlineStr">
         <is>
-          <t>FLM</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="F292" s="58" t="n"/>
       <c r="G292" s="58" t="n"/>
       <c r="H292" s="60" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I292" s="60" t="n">
         <v>36</v>
@@ -17208,7 +17142,7 @@
     <row r="293">
       <c r="A293" s="58" t="inlineStr">
         <is>
-          <t>R3-01-A</t>
+          <t>R3-01-B</t>
         </is>
       </c>
       <c r="B293" s="60" t="inlineStr">
@@ -17221,7 +17155,7 @@
       </c>
       <c r="D293" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E293" s="60" t="inlineStr">
@@ -17232,7 +17166,7 @@
       <c r="F293" s="58" t="n"/>
       <c r="G293" s="58" t="n"/>
       <c r="H293" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I293" s="60" t="n">
         <v>21</v>
@@ -17241,7 +17175,7 @@
     <row r="294">
       <c r="A294" s="58" t="inlineStr">
         <is>
-          <t>R3-02-A</t>
+          <t>R3-02-B</t>
         </is>
       </c>
       <c r="B294" s="60" t="inlineStr">
@@ -17254,7 +17188,7 @@
       </c>
       <c r="D294" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E294" s="60" t="inlineStr">
@@ -17265,7 +17199,7 @@
       <c r="F294" s="58" t="n"/>
       <c r="G294" s="58" t="n"/>
       <c r="H294" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I294" s="60" t="n">
         <v>22</v>
@@ -17274,7 +17208,7 @@
     <row r="295">
       <c r="A295" s="58" t="inlineStr">
         <is>
-          <t>R3-03-A</t>
+          <t>R3-03-B</t>
         </is>
       </c>
       <c r="B295" s="60" t="inlineStr">
@@ -17287,7 +17221,7 @@
       </c>
       <c r="D295" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E295" s="60" t="inlineStr">
@@ -17298,7 +17232,7 @@
       <c r="F295" s="58" t="n"/>
       <c r="G295" s="58" t="n"/>
       <c r="H295" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I295" s="60" t="n">
         <v>23</v>
@@ -17307,7 +17241,7 @@
     <row r="296">
       <c r="A296" s="58" t="inlineStr">
         <is>
-          <t>R3-04-A</t>
+          <t>R3-04-B</t>
         </is>
       </c>
       <c r="B296" s="60" t="inlineStr">
@@ -17320,7 +17254,7 @@
       </c>
       <c r="D296" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E296" s="60" t="inlineStr">
@@ -17331,7 +17265,7 @@
       <c r="F296" s="58" t="n"/>
       <c r="G296" s="58" t="n"/>
       <c r="H296" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I296" s="60" t="n">
         <v>24</v>
@@ -17340,7 +17274,7 @@
     <row r="297">
       <c r="A297" s="58" t="inlineStr">
         <is>
-          <t>R3-05-A</t>
+          <t>R3-05-B</t>
         </is>
       </c>
       <c r="B297" s="60" t="inlineStr">
@@ -17353,7 +17287,7 @@
       </c>
       <c r="D297" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E297" s="60" t="inlineStr">
@@ -17364,7 +17298,7 @@
       <c r="F297" s="58" t="n"/>
       <c r="G297" s="58" t="n"/>
       <c r="H297" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I297" s="60" t="n">
         <v>25</v>
@@ -17373,7 +17307,7 @@
     <row r="298">
       <c r="A298" s="58" t="inlineStr">
         <is>
-          <t>R3-06-A</t>
+          <t>R3-06-B</t>
         </is>
       </c>
       <c r="B298" s="60" t="inlineStr">
@@ -17386,7 +17320,7 @@
       </c>
       <c r="D298" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E298" s="60" t="inlineStr">
@@ -17397,7 +17331,7 @@
       <c r="F298" s="58" t="n"/>
       <c r="G298" s="58" t="n"/>
       <c r="H298" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I298" s="60" t="n">
         <v>26</v>
@@ -17406,7 +17340,7 @@
     <row r="299">
       <c r="A299" s="58" t="inlineStr">
         <is>
-          <t>R3-07-A</t>
+          <t>R3-07-B</t>
         </is>
       </c>
       <c r="B299" s="60" t="inlineStr">
@@ -17419,7 +17353,7 @@
       </c>
       <c r="D299" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E299" s="60" t="inlineStr">
@@ -17430,7 +17364,7 @@
       <c r="F299" s="58" t="n"/>
       <c r="G299" s="58" t="n"/>
       <c r="H299" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I299" s="60" t="n">
         <v>27</v>
@@ -17439,7 +17373,7 @@
     <row r="300">
       <c r="A300" s="58" t="inlineStr">
         <is>
-          <t>R3-08-A</t>
+          <t>R3-08-B</t>
         </is>
       </c>
       <c r="B300" s="60" t="inlineStr">
@@ -17452,7 +17386,7 @@
       </c>
       <c r="D300" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E300" s="60" t="inlineStr">
@@ -17463,7 +17397,7 @@
       <c r="F300" s="58" t="n"/>
       <c r="G300" s="58" t="n"/>
       <c r="H300" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I300" s="60" t="n">
         <v>28</v>
@@ -17472,7 +17406,7 @@
     <row r="301">
       <c r="A301" s="58" t="inlineStr">
         <is>
-          <t>R3-09-A</t>
+          <t>R3-09-B</t>
         </is>
       </c>
       <c r="B301" s="60" t="inlineStr">
@@ -17485,7 +17419,7 @@
       </c>
       <c r="D301" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E301" s="60" t="inlineStr">
@@ -17496,7 +17430,7 @@
       <c r="F301" s="58" t="n"/>
       <c r="G301" s="58" t="n"/>
       <c r="H301" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I301" s="60" t="n">
         <v>29</v>
@@ -17505,7 +17439,7 @@
     <row r="302">
       <c r="A302" s="58" t="inlineStr">
         <is>
-          <t>R3-10-A</t>
+          <t>R3-10-B</t>
         </is>
       </c>
       <c r="B302" s="60" t="inlineStr">
@@ -17518,7 +17452,7 @@
       </c>
       <c r="D302" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E302" s="60" t="inlineStr">
@@ -17529,7 +17463,7 @@
       <c r="F302" s="58" t="n"/>
       <c r="G302" s="58" t="n"/>
       <c r="H302" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I302" s="60" t="n">
         <v>30</v>
@@ -17538,7 +17472,7 @@
     <row r="303">
       <c r="A303" s="58" t="inlineStr">
         <is>
-          <t>R3-11-A</t>
+          <t>R3-11-B</t>
         </is>
       </c>
       <c r="B303" s="60" t="inlineStr">
@@ -17551,7 +17485,7 @@
       </c>
       <c r="D303" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E303" s="60" t="inlineStr">
@@ -17562,7 +17496,7 @@
       <c r="F303" s="58" t="n"/>
       <c r="G303" s="58" t="n"/>
       <c r="H303" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I303" s="60" t="n">
         <v>31</v>
@@ -17571,7 +17505,7 @@
     <row r="304">
       <c r="A304" s="58" t="inlineStr">
         <is>
-          <t>R3-12-A</t>
+          <t>R3-12-B</t>
         </is>
       </c>
       <c r="B304" s="60" t="inlineStr">
@@ -17584,7 +17518,7 @@
       </c>
       <c r="D304" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E304" s="60" t="inlineStr">
@@ -17595,7 +17529,7 @@
       <c r="F304" s="58" t="n"/>
       <c r="G304" s="58" t="n"/>
       <c r="H304" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I304" s="60" t="n">
         <v>32</v>
@@ -17604,7 +17538,7 @@
     <row r="305">
       <c r="A305" s="58" t="inlineStr">
         <is>
-          <t>R3-13-A</t>
+          <t>R3-13-B</t>
         </is>
       </c>
       <c r="B305" s="60" t="inlineStr">
@@ -17617,7 +17551,7 @@
       </c>
       <c r="D305" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E305" s="60" t="inlineStr">
@@ -17628,7 +17562,7 @@
       <c r="F305" s="58" t="n"/>
       <c r="G305" s="58" t="n"/>
       <c r="H305" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I305" s="60" t="n">
         <v>33</v>
@@ -17637,7 +17571,7 @@
     <row r="306">
       <c r="A306" s="58" t="inlineStr">
         <is>
-          <t>R3-14-A</t>
+          <t>R3-14-B</t>
         </is>
       </c>
       <c r="B306" s="60" t="inlineStr">
@@ -17650,7 +17584,7 @@
       </c>
       <c r="D306" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E306" s="60" t="inlineStr">
@@ -17661,7 +17595,7 @@
       <c r="F306" s="58" t="n"/>
       <c r="G306" s="58" t="n"/>
       <c r="H306" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I306" s="60" t="n">
         <v>34</v>
@@ -17670,7 +17604,7 @@
     <row r="307">
       <c r="A307" s="58" t="inlineStr">
         <is>
-          <t>R3-15-A</t>
+          <t>R3-15-B</t>
         </is>
       </c>
       <c r="B307" s="60" t="inlineStr">
@@ -17683,7 +17617,7 @@
       </c>
       <c r="D307" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E307" s="60" t="inlineStr">
@@ -17694,7 +17628,7 @@
       <c r="F307" s="58" t="n"/>
       <c r="G307" s="58" t="n"/>
       <c r="H307" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I307" s="60" t="n">
         <v>35</v>
@@ -17703,7 +17637,7 @@
     <row r="308">
       <c r="A308" s="58" t="inlineStr">
         <is>
-          <t>R3-16-A</t>
+          <t>R3-16-B</t>
         </is>
       </c>
       <c r="B308" s="60" t="inlineStr">
@@ -17716,7 +17650,7 @@
       </c>
       <c r="D308" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E308" s="60" t="inlineStr">
@@ -17727,7 +17661,7 @@
       <c r="F308" s="58" t="n"/>
       <c r="G308" s="58" t="n"/>
       <c r="H308" s="60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I308" s="60" t="n">
         <v>36</v>
@@ -17736,7 +17670,7 @@
     <row r="309">
       <c r="A309" s="58" t="inlineStr">
         <is>
-          <t>R3-01-B</t>
+          <t>R3-01-C</t>
         </is>
       </c>
       <c r="B309" s="60" t="inlineStr">
@@ -17749,7 +17683,7 @@
       </c>
       <c r="D309" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E309" s="60" t="inlineStr">
@@ -17760,7 +17694,7 @@
       <c r="F309" s="58" t="n"/>
       <c r="G309" s="58" t="n"/>
       <c r="H309" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I309" s="60" t="n">
         <v>21</v>
@@ -17769,7 +17703,7 @@
     <row r="310">
       <c r="A310" s="58" t="inlineStr">
         <is>
-          <t>R3-02-B</t>
+          <t>R3-02-C</t>
         </is>
       </c>
       <c r="B310" s="60" t="inlineStr">
@@ -17782,7 +17716,7 @@
       </c>
       <c r="D310" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E310" s="60" t="inlineStr">
@@ -17793,7 +17727,7 @@
       <c r="F310" s="58" t="n"/>
       <c r="G310" s="58" t="n"/>
       <c r="H310" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I310" s="60" t="n">
         <v>22</v>
@@ -17802,7 +17736,7 @@
     <row r="311">
       <c r="A311" s="58" t="inlineStr">
         <is>
-          <t>R3-03-B</t>
+          <t>R3-03-C</t>
         </is>
       </c>
       <c r="B311" s="60" t="inlineStr">
@@ -17815,7 +17749,7 @@
       </c>
       <c r="D311" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E311" s="60" t="inlineStr">
@@ -17826,7 +17760,7 @@
       <c r="F311" s="58" t="n"/>
       <c r="G311" s="58" t="n"/>
       <c r="H311" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I311" s="60" t="n">
         <v>23</v>
@@ -17835,7 +17769,7 @@
     <row r="312">
       <c r="A312" s="58" t="inlineStr">
         <is>
-          <t>R3-04-B</t>
+          <t>R3-04-C</t>
         </is>
       </c>
       <c r="B312" s="60" t="inlineStr">
@@ -17848,7 +17782,7 @@
       </c>
       <c r="D312" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E312" s="60" t="inlineStr">
@@ -17859,7 +17793,7 @@
       <c r="F312" s="58" t="n"/>
       <c r="G312" s="58" t="n"/>
       <c r="H312" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I312" s="60" t="n">
         <v>24</v>
@@ -17868,7 +17802,7 @@
     <row r="313">
       <c r="A313" s="58" t="inlineStr">
         <is>
-          <t>R3-05-B</t>
+          <t>R3-05-C</t>
         </is>
       </c>
       <c r="B313" s="60" t="inlineStr">
@@ -17881,7 +17815,7 @@
       </c>
       <c r="D313" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E313" s="60" t="inlineStr">
@@ -17892,7 +17826,7 @@
       <c r="F313" s="58" t="n"/>
       <c r="G313" s="58" t="n"/>
       <c r="H313" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I313" s="60" t="n">
         <v>25</v>
@@ -17901,7 +17835,7 @@
     <row r="314">
       <c r="A314" s="58" t="inlineStr">
         <is>
-          <t>R3-06-B</t>
+          <t>R3-06-C</t>
         </is>
       </c>
       <c r="B314" s="60" t="inlineStr">
@@ -17914,7 +17848,7 @@
       </c>
       <c r="D314" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E314" s="60" t="inlineStr">
@@ -17925,7 +17859,7 @@
       <c r="F314" s="58" t="n"/>
       <c r="G314" s="58" t="n"/>
       <c r="H314" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I314" s="60" t="n">
         <v>26</v>
@@ -17934,7 +17868,7 @@
     <row r="315">
       <c r="A315" s="58" t="inlineStr">
         <is>
-          <t>R3-07-B</t>
+          <t>R3-07-C</t>
         </is>
       </c>
       <c r="B315" s="60" t="inlineStr">
@@ -17947,7 +17881,7 @@
       </c>
       <c r="D315" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E315" s="60" t="inlineStr">
@@ -17958,7 +17892,7 @@
       <c r="F315" s="58" t="n"/>
       <c r="G315" s="58" t="n"/>
       <c r="H315" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I315" s="60" t="n">
         <v>27</v>
@@ -17967,7 +17901,7 @@
     <row r="316">
       <c r="A316" s="58" t="inlineStr">
         <is>
-          <t>R3-08-B</t>
+          <t>R3-08-C</t>
         </is>
       </c>
       <c r="B316" s="60" t="inlineStr">
@@ -17980,7 +17914,7 @@
       </c>
       <c r="D316" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E316" s="60" t="inlineStr">
@@ -17991,7 +17925,7 @@
       <c r="F316" s="58" t="n"/>
       <c r="G316" s="58" t="n"/>
       <c r="H316" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I316" s="60" t="n">
         <v>28</v>
@@ -18000,7 +17934,7 @@
     <row r="317">
       <c r="A317" s="58" t="inlineStr">
         <is>
-          <t>R3-09-B</t>
+          <t>R3-09-C</t>
         </is>
       </c>
       <c r="B317" s="60" t="inlineStr">
@@ -18013,7 +17947,7 @@
       </c>
       <c r="D317" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E317" s="60" t="inlineStr">
@@ -18024,7 +17958,7 @@
       <c r="F317" s="58" t="n"/>
       <c r="G317" s="58" t="n"/>
       <c r="H317" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I317" s="60" t="n">
         <v>29</v>
@@ -18033,7 +17967,7 @@
     <row r="318">
       <c r="A318" s="58" t="inlineStr">
         <is>
-          <t>R3-10-B</t>
+          <t>R3-10-C</t>
         </is>
       </c>
       <c r="B318" s="60" t="inlineStr">
@@ -18046,7 +17980,7 @@
       </c>
       <c r="D318" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E318" s="60" t="inlineStr">
@@ -18057,7 +17991,7 @@
       <c r="F318" s="58" t="n"/>
       <c r="G318" s="58" t="n"/>
       <c r="H318" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I318" s="60" t="n">
         <v>30</v>
@@ -18066,7 +18000,7 @@
     <row r="319">
       <c r="A319" s="58" t="inlineStr">
         <is>
-          <t>R3-11-B</t>
+          <t>R3-11-C</t>
         </is>
       </c>
       <c r="B319" s="60" t="inlineStr">
@@ -18079,7 +18013,7 @@
       </c>
       <c r="D319" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E319" s="60" t="inlineStr">
@@ -18090,7 +18024,7 @@
       <c r="F319" s="58" t="n"/>
       <c r="G319" s="58" t="n"/>
       <c r="H319" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I319" s="60" t="n">
         <v>31</v>
@@ -18099,7 +18033,7 @@
     <row r="320">
       <c r="A320" s="58" t="inlineStr">
         <is>
-          <t>R3-12-B</t>
+          <t>R3-12-C</t>
         </is>
       </c>
       <c r="B320" s="60" t="inlineStr">
@@ -18112,7 +18046,7 @@
       </c>
       <c r="D320" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E320" s="60" t="inlineStr">
@@ -18123,7 +18057,7 @@
       <c r="F320" s="58" t="n"/>
       <c r="G320" s="58" t="n"/>
       <c r="H320" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I320" s="60" t="n">
         <v>32</v>
@@ -18132,7 +18066,7 @@
     <row r="321">
       <c r="A321" s="58" t="inlineStr">
         <is>
-          <t>R3-13-B</t>
+          <t>R3-13-C</t>
         </is>
       </c>
       <c r="B321" s="60" t="inlineStr">
@@ -18145,7 +18079,7 @@
       </c>
       <c r="D321" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E321" s="60" t="inlineStr">
@@ -18156,7 +18090,7 @@
       <c r="F321" s="58" t="n"/>
       <c r="G321" s="58" t="n"/>
       <c r="H321" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I321" s="60" t="n">
         <v>33</v>
@@ -18165,7 +18099,7 @@
     <row r="322">
       <c r="A322" s="58" t="inlineStr">
         <is>
-          <t>R3-14-B</t>
+          <t>R3-14-C</t>
         </is>
       </c>
       <c r="B322" s="60" t="inlineStr">
@@ -18178,7 +18112,7 @@
       </c>
       <c r="D322" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E322" s="60" t="inlineStr">
@@ -18189,7 +18123,7 @@
       <c r="F322" s="58" t="n"/>
       <c r="G322" s="58" t="n"/>
       <c r="H322" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I322" s="60" t="n">
         <v>34</v>
@@ -18198,7 +18132,7 @@
     <row r="323">
       <c r="A323" s="58" t="inlineStr">
         <is>
-          <t>R3-15-B</t>
+          <t>R3-15-C</t>
         </is>
       </c>
       <c r="B323" s="60" t="inlineStr">
@@ -18211,7 +18145,7 @@
       </c>
       <c r="D323" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E323" s="60" t="inlineStr">
@@ -18222,7 +18156,7 @@
       <c r="F323" s="58" t="n"/>
       <c r="G323" s="58" t="n"/>
       <c r="H323" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I323" s="60" t="n">
         <v>35</v>
@@ -18231,7 +18165,7 @@
     <row r="324">
       <c r="A324" s="58" t="inlineStr">
         <is>
-          <t>R3-16-B</t>
+          <t>R3-16-C</t>
         </is>
       </c>
       <c r="B324" s="60" t="inlineStr">
@@ -18244,7 +18178,7 @@
       </c>
       <c r="D324" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E324" s="60" t="inlineStr">
@@ -18255,7 +18189,7 @@
       <c r="F324" s="58" t="n"/>
       <c r="G324" s="58" t="n"/>
       <c r="H324" s="60" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I324" s="60" t="n">
         <v>36</v>
@@ -18264,7 +18198,7 @@
     <row r="325">
       <c r="A325" s="58" t="inlineStr">
         <is>
-          <t>R3-01-C</t>
+          <t>R3-01-D</t>
         </is>
       </c>
       <c r="B325" s="60" t="inlineStr">
@@ -18277,7 +18211,7 @@
       </c>
       <c r="D325" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E325" s="60" t="inlineStr">
@@ -18288,7 +18222,7 @@
       <c r="F325" s="58" t="n"/>
       <c r="G325" s="58" t="n"/>
       <c r="H325" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I325" s="60" t="n">
         <v>21</v>
@@ -18297,7 +18231,7 @@
     <row r="326">
       <c r="A326" s="58" t="inlineStr">
         <is>
-          <t>R3-02-C</t>
+          <t>R3-02-D</t>
         </is>
       </c>
       <c r="B326" s="60" t="inlineStr">
@@ -18310,7 +18244,7 @@
       </c>
       <c r="D326" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E326" s="60" t="inlineStr">
@@ -18321,7 +18255,7 @@
       <c r="F326" s="58" t="n"/>
       <c r="G326" s="58" t="n"/>
       <c r="H326" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I326" s="60" t="n">
         <v>22</v>
@@ -18330,7 +18264,7 @@
     <row r="327">
       <c r="A327" s="58" t="inlineStr">
         <is>
-          <t>R3-03-C</t>
+          <t>R3-03-D</t>
         </is>
       </c>
       <c r="B327" s="60" t="inlineStr">
@@ -18343,7 +18277,7 @@
       </c>
       <c r="D327" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E327" s="60" t="inlineStr">
@@ -18354,7 +18288,7 @@
       <c r="F327" s="58" t="n"/>
       <c r="G327" s="58" t="n"/>
       <c r="H327" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I327" s="60" t="n">
         <v>23</v>
@@ -18363,7 +18297,7 @@
     <row r="328">
       <c r="A328" s="58" t="inlineStr">
         <is>
-          <t>R3-04-C</t>
+          <t>R3-04-D</t>
         </is>
       </c>
       <c r="B328" s="60" t="inlineStr">
@@ -18376,7 +18310,7 @@
       </c>
       <c r="D328" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E328" s="60" t="inlineStr">
@@ -18387,7 +18321,7 @@
       <c r="F328" s="58" t="n"/>
       <c r="G328" s="58" t="n"/>
       <c r="H328" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I328" s="60" t="n">
         <v>24</v>
@@ -18396,7 +18330,7 @@
     <row r="329">
       <c r="A329" s="58" t="inlineStr">
         <is>
-          <t>R3-05-C</t>
+          <t>R3-05-D</t>
         </is>
       </c>
       <c r="B329" s="60" t="inlineStr">
@@ -18409,7 +18343,7 @@
       </c>
       <c r="D329" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E329" s="60" t="inlineStr">
@@ -18420,7 +18354,7 @@
       <c r="F329" s="58" t="n"/>
       <c r="G329" s="58" t="n"/>
       <c r="H329" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I329" s="60" t="n">
         <v>25</v>
@@ -18429,7 +18363,7 @@
     <row r="330">
       <c r="A330" s="58" t="inlineStr">
         <is>
-          <t>R3-06-C</t>
+          <t>R3-06-D</t>
         </is>
       </c>
       <c r="B330" s="60" t="inlineStr">
@@ -18442,7 +18376,7 @@
       </c>
       <c r="D330" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E330" s="60" t="inlineStr">
@@ -18453,7 +18387,7 @@
       <c r="F330" s="58" t="n"/>
       <c r="G330" s="58" t="n"/>
       <c r="H330" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I330" s="60" t="n">
         <v>26</v>
@@ -18462,7 +18396,7 @@
     <row r="331">
       <c r="A331" s="58" t="inlineStr">
         <is>
-          <t>R3-07-C</t>
+          <t>R3-07-D</t>
         </is>
       </c>
       <c r="B331" s="60" t="inlineStr">
@@ -18475,7 +18409,7 @@
       </c>
       <c r="D331" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E331" s="60" t="inlineStr">
@@ -18486,7 +18420,7 @@
       <c r="F331" s="58" t="n"/>
       <c r="G331" s="58" t="n"/>
       <c r="H331" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I331" s="60" t="n">
         <v>27</v>
@@ -18495,7 +18429,7 @@
     <row r="332">
       <c r="A332" s="58" t="inlineStr">
         <is>
-          <t>R3-08-C</t>
+          <t>R3-08-D</t>
         </is>
       </c>
       <c r="B332" s="60" t="inlineStr">
@@ -18508,7 +18442,7 @@
       </c>
       <c r="D332" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E332" s="60" t="inlineStr">
@@ -18519,7 +18453,7 @@
       <c r="F332" s="58" t="n"/>
       <c r="G332" s="58" t="n"/>
       <c r="H332" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I332" s="60" t="n">
         <v>28</v>
@@ -18528,7 +18462,7 @@
     <row r="333">
       <c r="A333" s="58" t="inlineStr">
         <is>
-          <t>R3-09-C</t>
+          <t>R3-09-D</t>
         </is>
       </c>
       <c r="B333" s="60" t="inlineStr">
@@ -18541,7 +18475,7 @@
       </c>
       <c r="D333" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E333" s="60" t="inlineStr">
@@ -18552,7 +18486,7 @@
       <c r="F333" s="58" t="n"/>
       <c r="G333" s="58" t="n"/>
       <c r="H333" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I333" s="60" t="n">
         <v>29</v>
@@ -18561,7 +18495,7 @@
     <row r="334">
       <c r="A334" s="58" t="inlineStr">
         <is>
-          <t>R3-10-C</t>
+          <t>R3-10-D</t>
         </is>
       </c>
       <c r="B334" s="60" t="inlineStr">
@@ -18574,7 +18508,7 @@
       </c>
       <c r="D334" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E334" s="60" t="inlineStr">
@@ -18585,7 +18519,7 @@
       <c r="F334" s="58" t="n"/>
       <c r="G334" s="58" t="n"/>
       <c r="H334" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I334" s="60" t="n">
         <v>30</v>
@@ -18594,7 +18528,7 @@
     <row r="335">
       <c r="A335" s="58" t="inlineStr">
         <is>
-          <t>R3-11-C</t>
+          <t>R3-11-D</t>
         </is>
       </c>
       <c r="B335" s="60" t="inlineStr">
@@ -18607,7 +18541,7 @@
       </c>
       <c r="D335" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E335" s="60" t="inlineStr">
@@ -18618,7 +18552,7 @@
       <c r="F335" s="58" t="n"/>
       <c r="G335" s="58" t="n"/>
       <c r="H335" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I335" s="60" t="n">
         <v>31</v>
@@ -18627,7 +18561,7 @@
     <row r="336">
       <c r="A336" s="58" t="inlineStr">
         <is>
-          <t>R3-12-C</t>
+          <t>R3-12-D</t>
         </is>
       </c>
       <c r="B336" s="60" t="inlineStr">
@@ -18640,7 +18574,7 @@
       </c>
       <c r="D336" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E336" s="60" t="inlineStr">
@@ -18651,7 +18585,7 @@
       <c r="F336" s="58" t="n"/>
       <c r="G336" s="58" t="n"/>
       <c r="H336" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I336" s="60" t="n">
         <v>32</v>
@@ -18660,7 +18594,7 @@
     <row r="337">
       <c r="A337" s="58" t="inlineStr">
         <is>
-          <t>R3-13-C</t>
+          <t>R3-13-D</t>
         </is>
       </c>
       <c r="B337" s="60" t="inlineStr">
@@ -18673,7 +18607,7 @@
       </c>
       <c r="D337" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E337" s="60" t="inlineStr">
@@ -18684,7 +18618,7 @@
       <c r="F337" s="58" t="n"/>
       <c r="G337" s="58" t="n"/>
       <c r="H337" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I337" s="60" t="n">
         <v>33</v>
@@ -18693,7 +18627,7 @@
     <row r="338">
       <c r="A338" s="58" t="inlineStr">
         <is>
-          <t>R3-14-C</t>
+          <t>R3-14-D</t>
         </is>
       </c>
       <c r="B338" s="60" t="inlineStr">
@@ -18706,7 +18640,7 @@
       </c>
       <c r="D338" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E338" s="60" t="inlineStr">
@@ -18717,7 +18651,7 @@
       <c r="F338" s="58" t="n"/>
       <c r="G338" s="58" t="n"/>
       <c r="H338" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I338" s="60" t="n">
         <v>34</v>
@@ -18726,7 +18660,7 @@
     <row r="339">
       <c r="A339" s="58" t="inlineStr">
         <is>
-          <t>R3-15-C</t>
+          <t>R3-15-D</t>
         </is>
       </c>
       <c r="B339" s="60" t="inlineStr">
@@ -18739,7 +18673,7 @@
       </c>
       <c r="D339" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E339" s="60" t="inlineStr">
@@ -18750,7 +18684,7 @@
       <c r="F339" s="58" t="n"/>
       <c r="G339" s="58" t="n"/>
       <c r="H339" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I339" s="60" t="n">
         <v>35</v>
@@ -18759,7 +18693,7 @@
     <row r="340">
       <c r="A340" s="58" t="inlineStr">
         <is>
-          <t>R3-16-C</t>
+          <t>R3-16-D</t>
         </is>
       </c>
       <c r="B340" s="60" t="inlineStr">
@@ -18772,7 +18706,7 @@
       </c>
       <c r="D340" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E340" s="60" t="inlineStr">
@@ -18783,7 +18717,7 @@
       <c r="F340" s="58" t="n"/>
       <c r="G340" s="58" t="n"/>
       <c r="H340" s="60" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I340" s="60" t="n">
         <v>36</v>
@@ -18792,12 +18726,12 @@
     <row r="341">
       <c r="A341" s="58" t="inlineStr">
         <is>
-          <t>R3-01-D</t>
+          <t>R4-01-A</t>
         </is>
       </c>
       <c r="B341" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C341" s="61" t="n">
@@ -18805,18 +18739,18 @@
       </c>
       <c r="D341" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E341" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F341" s="58" t="n"/>
       <c r="G341" s="58" t="n"/>
       <c r="H341" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I341" s="60" t="n">
         <v>21</v>
@@ -18825,12 +18759,12 @@
     <row r="342">
       <c r="A342" s="58" t="inlineStr">
         <is>
-          <t>R3-02-D</t>
+          <t>R4-02-A</t>
         </is>
       </c>
       <c r="B342" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C342" s="61" t="n">
@@ -18838,18 +18772,18 @@
       </c>
       <c r="D342" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E342" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F342" s="58" t="n"/>
       <c r="G342" s="58" t="n"/>
       <c r="H342" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I342" s="60" t="n">
         <v>22</v>
@@ -18858,12 +18792,12 @@
     <row r="343">
       <c r="A343" s="58" t="inlineStr">
         <is>
-          <t>R3-03-D</t>
+          <t>R4-03-A</t>
         </is>
       </c>
       <c r="B343" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C343" s="61" t="n">
@@ -18871,18 +18805,18 @@
       </c>
       <c r="D343" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E343" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F343" s="58" t="n"/>
       <c r="G343" s="58" t="n"/>
       <c r="H343" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I343" s="60" t="n">
         <v>23</v>
@@ -18891,12 +18825,12 @@
     <row r="344">
       <c r="A344" s="58" t="inlineStr">
         <is>
-          <t>R3-04-D</t>
+          <t>R4-04-A</t>
         </is>
       </c>
       <c r="B344" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C344" s="61" t="n">
@@ -18904,18 +18838,18 @@
       </c>
       <c r="D344" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E344" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F344" s="58" t="n"/>
       <c r="G344" s="58" t="n"/>
       <c r="H344" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I344" s="60" t="n">
         <v>24</v>
@@ -18924,12 +18858,12 @@
     <row r="345">
       <c r="A345" s="58" t="inlineStr">
         <is>
-          <t>R3-05-D</t>
+          <t>R4-05-A</t>
         </is>
       </c>
       <c r="B345" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C345" s="61" t="n">
@@ -18937,18 +18871,18 @@
       </c>
       <c r="D345" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E345" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F345" s="58" t="n"/>
       <c r="G345" s="58" t="n"/>
       <c r="H345" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I345" s="60" t="n">
         <v>25</v>
@@ -18957,12 +18891,12 @@
     <row r="346">
       <c r="A346" s="58" t="inlineStr">
         <is>
-          <t>R3-06-D</t>
+          <t>R4-06-A</t>
         </is>
       </c>
       <c r="B346" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C346" s="61" t="n">
@@ -18970,18 +18904,18 @@
       </c>
       <c r="D346" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E346" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F346" s="58" t="n"/>
       <c r="G346" s="58" t="n"/>
       <c r="H346" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I346" s="60" t="n">
         <v>26</v>
@@ -18990,12 +18924,12 @@
     <row r="347">
       <c r="A347" s="58" t="inlineStr">
         <is>
-          <t>R3-07-D</t>
+          <t>R4-07-A</t>
         </is>
       </c>
       <c r="B347" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C347" s="61" t="n">
@@ -19003,18 +18937,18 @@
       </c>
       <c r="D347" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E347" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F347" s="58" t="n"/>
       <c r="G347" s="58" t="n"/>
       <c r="H347" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I347" s="60" t="n">
         <v>27</v>
@@ -19023,12 +18957,12 @@
     <row r="348">
       <c r="A348" s="58" t="inlineStr">
         <is>
-          <t>R3-08-D</t>
+          <t>R4-08-A</t>
         </is>
       </c>
       <c r="B348" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C348" s="61" t="n">
@@ -19036,18 +18970,18 @@
       </c>
       <c r="D348" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E348" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F348" s="58" t="n"/>
       <c r="G348" s="58" t="n"/>
       <c r="H348" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I348" s="60" t="n">
         <v>28</v>
@@ -19056,12 +18990,12 @@
     <row r="349">
       <c r="A349" s="58" t="inlineStr">
         <is>
-          <t>R3-09-D</t>
+          <t>R4-09-A</t>
         </is>
       </c>
       <c r="B349" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C349" s="61" t="n">
@@ -19069,18 +19003,18 @@
       </c>
       <c r="D349" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E349" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F349" s="58" t="n"/>
       <c r="G349" s="58" t="n"/>
       <c r="H349" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I349" s="60" t="n">
         <v>29</v>
@@ -19089,12 +19023,12 @@
     <row r="350">
       <c r="A350" s="58" t="inlineStr">
         <is>
-          <t>R3-10-D</t>
+          <t>R4-10-A</t>
         </is>
       </c>
       <c r="B350" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C350" s="61" t="n">
@@ -19102,18 +19036,18 @@
       </c>
       <c r="D350" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E350" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F350" s="58" t="n"/>
       <c r="G350" s="58" t="n"/>
       <c r="H350" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I350" s="60" t="n">
         <v>30</v>
@@ -19122,12 +19056,12 @@
     <row r="351">
       <c r="A351" s="58" t="inlineStr">
         <is>
-          <t>R3-11-D</t>
+          <t>R4-11-A</t>
         </is>
       </c>
       <c r="B351" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C351" s="61" t="n">
@@ -19135,18 +19069,18 @@
       </c>
       <c r="D351" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E351" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F351" s="58" t="n"/>
       <c r="G351" s="58" t="n"/>
       <c r="H351" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I351" s="60" t="n">
         <v>31</v>
@@ -19155,12 +19089,12 @@
     <row r="352">
       <c r="A352" s="58" t="inlineStr">
         <is>
-          <t>R3-12-D</t>
+          <t>R4-12-A</t>
         </is>
       </c>
       <c r="B352" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C352" s="61" t="n">
@@ -19168,18 +19102,18 @@
       </c>
       <c r="D352" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E352" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F352" s="58" t="n"/>
       <c r="G352" s="58" t="n"/>
       <c r="H352" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I352" s="60" t="n">
         <v>32</v>
@@ -19188,12 +19122,12 @@
     <row r="353">
       <c r="A353" s="58" t="inlineStr">
         <is>
-          <t>R3-13-D</t>
+          <t>R4-13-A</t>
         </is>
       </c>
       <c r="B353" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C353" s="61" t="n">
@@ -19201,18 +19135,18 @@
       </c>
       <c r="D353" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E353" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F353" s="58" t="n"/>
       <c r="G353" s="58" t="n"/>
       <c r="H353" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I353" s="60" t="n">
         <v>33</v>
@@ -19221,12 +19155,12 @@
     <row r="354">
       <c r="A354" s="58" t="inlineStr">
         <is>
-          <t>R3-14-D</t>
+          <t>R4-14-A</t>
         </is>
       </c>
       <c r="B354" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C354" s="61" t="n">
@@ -19234,18 +19168,18 @@
       </c>
       <c r="D354" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E354" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F354" s="58" t="n"/>
       <c r="G354" s="58" t="n"/>
       <c r="H354" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I354" s="60" t="n">
         <v>34</v>
@@ -19254,12 +19188,12 @@
     <row r="355">
       <c r="A355" s="58" t="inlineStr">
         <is>
-          <t>R3-15-D</t>
+          <t>R4-15-A</t>
         </is>
       </c>
       <c r="B355" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C355" s="61" t="n">
@@ -19267,18 +19201,18 @@
       </c>
       <c r="D355" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E355" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F355" s="58" t="n"/>
       <c r="G355" s="58" t="n"/>
       <c r="H355" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I355" s="60" t="n">
         <v>35</v>
@@ -19287,12 +19221,12 @@
     <row r="356">
       <c r="A356" s="58" t="inlineStr">
         <is>
-          <t>R3-16-D</t>
+          <t>R4-16-A</t>
         </is>
       </c>
       <c r="B356" s="60" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="C356" s="61" t="n">
@@ -19300,18 +19234,18 @@
       </c>
       <c r="D356" s="60" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E356" s="60" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>BOX</t>
         </is>
       </c>
       <c r="F356" s="58" t="n"/>
       <c r="G356" s="58" t="n"/>
       <c r="H356" s="60" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I356" s="60" t="n">
         <v>36</v>
@@ -19320,7 +19254,7 @@
     <row r="357">
       <c r="A357" s="58" t="inlineStr">
         <is>
-          <t>R4-01-A</t>
+          <t>R4-01-B</t>
         </is>
       </c>
       <c r="B357" s="60" t="inlineStr">
@@ -19333,7 +19267,7 @@
       </c>
       <c r="D357" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E357" s="60" t="inlineStr">
@@ -19344,7 +19278,7 @@
       <c r="F357" s="58" t="n"/>
       <c r="G357" s="58" t="n"/>
       <c r="H357" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I357" s="60" t="n">
         <v>21</v>
@@ -19353,7 +19287,7 @@
     <row r="358">
       <c r="A358" s="58" t="inlineStr">
         <is>
-          <t>R4-02-A</t>
+          <t>R4-02-B</t>
         </is>
       </c>
       <c r="B358" s="60" t="inlineStr">
@@ -19366,7 +19300,7 @@
       </c>
       <c r="D358" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E358" s="60" t="inlineStr">
@@ -19377,7 +19311,7 @@
       <c r="F358" s="58" t="n"/>
       <c r="G358" s="58" t="n"/>
       <c r="H358" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I358" s="60" t="n">
         <v>22</v>
@@ -19386,7 +19320,7 @@
     <row r="359">
       <c r="A359" s="58" t="inlineStr">
         <is>
-          <t>R4-03-A</t>
+          <t>R4-03-B</t>
         </is>
       </c>
       <c r="B359" s="60" t="inlineStr">
@@ -19399,7 +19333,7 @@
       </c>
       <c r="D359" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E359" s="60" t="inlineStr">
@@ -19410,7 +19344,7 @@
       <c r="F359" s="58" t="n"/>
       <c r="G359" s="58" t="n"/>
       <c r="H359" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I359" s="60" t="n">
         <v>23</v>
@@ -19419,7 +19353,7 @@
     <row r="360">
       <c r="A360" s="58" t="inlineStr">
         <is>
-          <t>R4-04-A</t>
+          <t>R4-04-B</t>
         </is>
       </c>
       <c r="B360" s="60" t="inlineStr">
@@ -19432,7 +19366,7 @@
       </c>
       <c r="D360" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E360" s="60" t="inlineStr">
@@ -19443,7 +19377,7 @@
       <c r="F360" s="58" t="n"/>
       <c r="G360" s="58" t="n"/>
       <c r="H360" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I360" s="60" t="n">
         <v>24</v>
@@ -19452,7 +19386,7 @@
     <row r="361">
       <c r="A361" s="58" t="inlineStr">
         <is>
-          <t>R4-05-A</t>
+          <t>R4-05-B</t>
         </is>
       </c>
       <c r="B361" s="60" t="inlineStr">
@@ -19465,7 +19399,7 @@
       </c>
       <c r="D361" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E361" s="60" t="inlineStr">
@@ -19476,7 +19410,7 @@
       <c r="F361" s="58" t="n"/>
       <c r="G361" s="58" t="n"/>
       <c r="H361" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I361" s="60" t="n">
         <v>25</v>
@@ -19485,7 +19419,7 @@
     <row r="362">
       <c r="A362" s="58" t="inlineStr">
         <is>
-          <t>R4-06-A</t>
+          <t>R4-06-B</t>
         </is>
       </c>
       <c r="B362" s="60" t="inlineStr">
@@ -19498,7 +19432,7 @@
       </c>
       <c r="D362" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E362" s="60" t="inlineStr">
@@ -19509,7 +19443,7 @@
       <c r="F362" s="58" t="n"/>
       <c r="G362" s="58" t="n"/>
       <c r="H362" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I362" s="60" t="n">
         <v>26</v>
@@ -19518,7 +19452,7 @@
     <row r="363">
       <c r="A363" s="58" t="inlineStr">
         <is>
-          <t>R4-07-A</t>
+          <t>R4-07-B</t>
         </is>
       </c>
       <c r="B363" s="60" t="inlineStr">
@@ -19531,7 +19465,7 @@
       </c>
       <c r="D363" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E363" s="60" t="inlineStr">
@@ -19542,7 +19476,7 @@
       <c r="F363" s="58" t="n"/>
       <c r="G363" s="58" t="n"/>
       <c r="H363" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I363" s="60" t="n">
         <v>27</v>
@@ -19551,7 +19485,7 @@
     <row r="364">
       <c r="A364" s="58" t="inlineStr">
         <is>
-          <t>R4-08-A</t>
+          <t>R4-08-B</t>
         </is>
       </c>
       <c r="B364" s="60" t="inlineStr">
@@ -19564,7 +19498,7 @@
       </c>
       <c r="D364" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E364" s="60" t="inlineStr">
@@ -19575,7 +19509,7 @@
       <c r="F364" s="58" t="n"/>
       <c r="G364" s="58" t="n"/>
       <c r="H364" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I364" s="60" t="n">
         <v>28</v>
@@ -19584,7 +19518,7 @@
     <row r="365">
       <c r="A365" s="58" t="inlineStr">
         <is>
-          <t>R4-09-A</t>
+          <t>R4-09-B</t>
         </is>
       </c>
       <c r="B365" s="60" t="inlineStr">
@@ -19597,7 +19531,7 @@
       </c>
       <c r="D365" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E365" s="60" t="inlineStr">
@@ -19608,7 +19542,7 @@
       <c r="F365" s="58" t="n"/>
       <c r="G365" s="58" t="n"/>
       <c r="H365" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I365" s="60" t="n">
         <v>29</v>
@@ -19617,7 +19551,7 @@
     <row r="366">
       <c r="A366" s="58" t="inlineStr">
         <is>
-          <t>R4-10-A</t>
+          <t>R4-10-B</t>
         </is>
       </c>
       <c r="B366" s="60" t="inlineStr">
@@ -19630,7 +19564,7 @@
       </c>
       <c r="D366" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E366" s="60" t="inlineStr">
@@ -19641,7 +19575,7 @@
       <c r="F366" s="58" t="n"/>
       <c r="G366" s="58" t="n"/>
       <c r="H366" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I366" s="60" t="n">
         <v>30</v>
@@ -19650,7 +19584,7 @@
     <row r="367">
       <c r="A367" s="58" t="inlineStr">
         <is>
-          <t>R4-11-A</t>
+          <t>R4-11-B</t>
         </is>
       </c>
       <c r="B367" s="60" t="inlineStr">
@@ -19663,7 +19597,7 @@
       </c>
       <c r="D367" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E367" s="60" t="inlineStr">
@@ -19674,7 +19608,7 @@
       <c r="F367" s="58" t="n"/>
       <c r="G367" s="58" t="n"/>
       <c r="H367" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I367" s="60" t="n">
         <v>31</v>
@@ -19683,7 +19617,7 @@
     <row r="368">
       <c r="A368" s="58" t="inlineStr">
         <is>
-          <t>R4-12-A</t>
+          <t>R4-12-B</t>
         </is>
       </c>
       <c r="B368" s="60" t="inlineStr">
@@ -19696,7 +19630,7 @@
       </c>
       <c r="D368" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E368" s="60" t="inlineStr">
@@ -19707,7 +19641,7 @@
       <c r="F368" s="58" t="n"/>
       <c r="G368" s="58" t="n"/>
       <c r="H368" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I368" s="60" t="n">
         <v>32</v>
@@ -19716,7 +19650,7 @@
     <row r="369">
       <c r="A369" s="58" t="inlineStr">
         <is>
-          <t>R4-13-A</t>
+          <t>R4-13-B</t>
         </is>
       </c>
       <c r="B369" s="60" t="inlineStr">
@@ -19729,7 +19663,7 @@
       </c>
       <c r="D369" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E369" s="60" t="inlineStr">
@@ -19740,7 +19674,7 @@
       <c r="F369" s="58" t="n"/>
       <c r="G369" s="58" t="n"/>
       <c r="H369" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I369" s="60" t="n">
         <v>33</v>
@@ -19749,7 +19683,7 @@
     <row r="370">
       <c r="A370" s="58" t="inlineStr">
         <is>
-          <t>R4-14-A</t>
+          <t>R4-14-B</t>
         </is>
       </c>
       <c r="B370" s="60" t="inlineStr">
@@ -19762,7 +19696,7 @@
       </c>
       <c r="D370" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E370" s="60" t="inlineStr">
@@ -19773,7 +19707,7 @@
       <c r="F370" s="58" t="n"/>
       <c r="G370" s="58" t="n"/>
       <c r="H370" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I370" s="60" t="n">
         <v>34</v>
@@ -19782,7 +19716,7 @@
     <row r="371">
       <c r="A371" s="58" t="inlineStr">
         <is>
-          <t>R4-15-A</t>
+          <t>R4-15-B</t>
         </is>
       </c>
       <c r="B371" s="60" t="inlineStr">
@@ -19795,7 +19729,7 @@
       </c>
       <c r="D371" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E371" s="60" t="inlineStr">
@@ -19806,7 +19740,7 @@
       <c r="F371" s="58" t="n"/>
       <c r="G371" s="58" t="n"/>
       <c r="H371" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I371" s="60" t="n">
         <v>35</v>
@@ -19815,7 +19749,7 @@
     <row r="372">
       <c r="A372" s="58" t="inlineStr">
         <is>
-          <t>R4-16-A</t>
+          <t>R4-16-B</t>
         </is>
       </c>
       <c r="B372" s="60" t="inlineStr">
@@ -19828,7 +19762,7 @@
       </c>
       <c r="D372" s="60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E372" s="60" t="inlineStr">
@@ -19839,7 +19773,7 @@
       <c r="F372" s="58" t="n"/>
       <c r="G372" s="58" t="n"/>
       <c r="H372" s="60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I372" s="60" t="n">
         <v>36</v>
@@ -19848,7 +19782,7 @@
     <row r="373">
       <c r="A373" s="58" t="inlineStr">
         <is>
-          <t>R4-01-B</t>
+          <t>R4-01-C</t>
         </is>
       </c>
       <c r="B373" s="60" t="inlineStr">
@@ -19861,7 +19795,7 @@
       </c>
       <c r="D373" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E373" s="60" t="inlineStr">
@@ -19872,7 +19806,7 @@
       <c r="F373" s="58" t="n"/>
       <c r="G373" s="58" t="n"/>
       <c r="H373" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I373" s="60" t="n">
         <v>21</v>
@@ -19881,7 +19815,7 @@
     <row r="374">
       <c r="A374" s="58" t="inlineStr">
         <is>
-          <t>R4-02-B</t>
+          <t>R4-02-C</t>
         </is>
       </c>
       <c r="B374" s="60" t="inlineStr">
@@ -19894,7 +19828,7 @@
       </c>
       <c r="D374" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E374" s="60" t="inlineStr">
@@ -19905,7 +19839,7 @@
       <c r="F374" s="58" t="n"/>
       <c r="G374" s="58" t="n"/>
       <c r="H374" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I374" s="60" t="n">
         <v>22</v>
@@ -19914,7 +19848,7 @@
     <row r="375">
       <c r="A375" s="58" t="inlineStr">
         <is>
-          <t>R4-03-B</t>
+          <t>R4-03-C</t>
         </is>
       </c>
       <c r="B375" s="60" t="inlineStr">
@@ -19927,7 +19861,7 @@
       </c>
       <c r="D375" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E375" s="60" t="inlineStr">
@@ -19938,7 +19872,7 @@
       <c r="F375" s="58" t="n"/>
       <c r="G375" s="58" t="n"/>
       <c r="H375" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I375" s="60" t="n">
         <v>23</v>
@@ -19947,7 +19881,7 @@
     <row r="376">
       <c r="A376" s="58" t="inlineStr">
         <is>
-          <t>R4-04-B</t>
+          <t>R4-04-C</t>
         </is>
       </c>
       <c r="B376" s="60" t="inlineStr">
@@ -19960,7 +19894,7 @@
       </c>
       <c r="D376" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E376" s="60" t="inlineStr">
@@ -19971,7 +19905,7 @@
       <c r="F376" s="58" t="n"/>
       <c r="G376" s="58" t="n"/>
       <c r="H376" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I376" s="60" t="n">
         <v>24</v>
@@ -19980,7 +19914,7 @@
     <row r="377">
       <c r="A377" s="58" t="inlineStr">
         <is>
-          <t>R4-05-B</t>
+          <t>R4-05-C</t>
         </is>
       </c>
       <c r="B377" s="60" t="inlineStr">
@@ -19993,7 +19927,7 @@
       </c>
       <c r="D377" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E377" s="60" t="inlineStr">
@@ -20004,7 +19938,7 @@
       <c r="F377" s="58" t="n"/>
       <c r="G377" s="58" t="n"/>
       <c r="H377" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I377" s="60" t="n">
         <v>25</v>
@@ -20013,7 +19947,7 @@
     <row r="378">
       <c r="A378" s="58" t="inlineStr">
         <is>
-          <t>R4-06-B</t>
+          <t>R4-06-C</t>
         </is>
       </c>
       <c r="B378" s="60" t="inlineStr">
@@ -20026,7 +19960,7 @@
       </c>
       <c r="D378" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E378" s="60" t="inlineStr">
@@ -20037,7 +19971,7 @@
       <c r="F378" s="58" t="n"/>
       <c r="G378" s="58" t="n"/>
       <c r="H378" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I378" s="60" t="n">
         <v>26</v>
@@ -20046,7 +19980,7 @@
     <row r="379">
       <c r="A379" s="58" t="inlineStr">
         <is>
-          <t>R4-07-B</t>
+          <t>R4-07-C</t>
         </is>
       </c>
       <c r="B379" s="60" t="inlineStr">
@@ -20059,7 +19993,7 @@
       </c>
       <c r="D379" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E379" s="60" t="inlineStr">
@@ -20070,7 +20004,7 @@
       <c r="F379" s="58" t="n"/>
       <c r="G379" s="58" t="n"/>
       <c r="H379" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I379" s="60" t="n">
         <v>27</v>
@@ -20079,7 +20013,7 @@
     <row r="380">
       <c r="A380" s="58" t="inlineStr">
         <is>
-          <t>R4-08-B</t>
+          <t>R4-08-C</t>
         </is>
       </c>
       <c r="B380" s="60" t="inlineStr">
@@ -20092,7 +20026,7 @@
       </c>
       <c r="D380" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E380" s="60" t="inlineStr">
@@ -20103,7 +20037,7 @@
       <c r="F380" s="58" t="n"/>
       <c r="G380" s="58" t="n"/>
       <c r="H380" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I380" s="60" t="n">
         <v>28</v>
@@ -20112,7 +20046,7 @@
     <row r="381">
       <c r="A381" s="58" t="inlineStr">
         <is>
-          <t>R4-09-B</t>
+          <t>R4-09-C</t>
         </is>
       </c>
       <c r="B381" s="60" t="inlineStr">
@@ -20125,7 +20059,7 @@
       </c>
       <c r="D381" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E381" s="60" t="inlineStr">
@@ -20136,7 +20070,7 @@
       <c r="F381" s="58" t="n"/>
       <c r="G381" s="58" t="n"/>
       <c r="H381" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I381" s="60" t="n">
         <v>29</v>
@@ -20145,7 +20079,7 @@
     <row r="382">
       <c r="A382" s="58" t="inlineStr">
         <is>
-          <t>R4-10-B</t>
+          <t>R4-10-C</t>
         </is>
       </c>
       <c r="B382" s="60" t="inlineStr">
@@ -20158,7 +20092,7 @@
       </c>
       <c r="D382" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E382" s="60" t="inlineStr">
@@ -20169,7 +20103,7 @@
       <c r="F382" s="58" t="n"/>
       <c r="G382" s="58" t="n"/>
       <c r="H382" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I382" s="60" t="n">
         <v>30</v>
@@ -20178,7 +20112,7 @@
     <row r="383">
       <c r="A383" s="58" t="inlineStr">
         <is>
-          <t>R4-11-B</t>
+          <t>R4-11-C</t>
         </is>
       </c>
       <c r="B383" s="60" t="inlineStr">
@@ -20191,7 +20125,7 @@
       </c>
       <c r="D383" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E383" s="60" t="inlineStr">
@@ -20202,7 +20136,7 @@
       <c r="F383" s="58" t="n"/>
       <c r="G383" s="58" t="n"/>
       <c r="H383" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I383" s="60" t="n">
         <v>31</v>
@@ -20211,7 +20145,7 @@
     <row r="384">
       <c r="A384" s="58" t="inlineStr">
         <is>
-          <t>R4-12-B</t>
+          <t>R4-12-C</t>
         </is>
       </c>
       <c r="B384" s="60" t="inlineStr">
@@ -20224,7 +20158,7 @@
       </c>
       <c r="D384" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E384" s="60" t="inlineStr">
@@ -20235,7 +20169,7 @@
       <c r="F384" s="58" t="n"/>
       <c r="G384" s="58" t="n"/>
       <c r="H384" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I384" s="60" t="n">
         <v>32</v>
@@ -20244,7 +20178,7 @@
     <row r="385">
       <c r="A385" s="58" t="inlineStr">
         <is>
-          <t>R4-13-B</t>
+          <t>R4-13-C</t>
         </is>
       </c>
       <c r="B385" s="60" t="inlineStr">
@@ -20257,7 +20191,7 @@
       </c>
       <c r="D385" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E385" s="60" t="inlineStr">
@@ -20268,7 +20202,7 @@
       <c r="F385" s="58" t="n"/>
       <c r="G385" s="58" t="n"/>
       <c r="H385" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I385" s="60" t="n">
         <v>33</v>
@@ -20277,7 +20211,7 @@
     <row r="386">
       <c r="A386" s="58" t="inlineStr">
         <is>
-          <t>R4-14-B</t>
+          <t>R4-14-C</t>
         </is>
       </c>
       <c r="B386" s="60" t="inlineStr">
@@ -20290,7 +20224,7 @@
       </c>
       <c r="D386" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E386" s="60" t="inlineStr">
@@ -20301,7 +20235,7 @@
       <c r="F386" s="58" t="n"/>
       <c r="G386" s="58" t="n"/>
       <c r="H386" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I386" s="60" t="n">
         <v>34</v>
@@ -20310,7 +20244,7 @@
     <row r="387">
       <c r="A387" s="58" t="inlineStr">
         <is>
-          <t>R4-15-B</t>
+          <t>R4-15-C</t>
         </is>
       </c>
       <c r="B387" s="60" t="inlineStr">
@@ -20323,7 +20257,7 @@
       </c>
       <c r="D387" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E387" s="60" t="inlineStr">
@@ -20334,7 +20268,7 @@
       <c r="F387" s="58" t="n"/>
       <c r="G387" s="58" t="n"/>
       <c r="H387" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I387" s="60" t="n">
         <v>35</v>
@@ -20343,7 +20277,7 @@
     <row r="388">
       <c r="A388" s="58" t="inlineStr">
         <is>
-          <t>R4-16-B</t>
+          <t>R4-16-C</t>
         </is>
       </c>
       <c r="B388" s="60" t="inlineStr">
@@ -20356,7 +20290,7 @@
       </c>
       <c r="D388" s="60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E388" s="60" t="inlineStr">
@@ -20367,7 +20301,7 @@
       <c r="F388" s="58" t="n"/>
       <c r="G388" s="58" t="n"/>
       <c r="H388" s="60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I388" s="60" t="n">
         <v>36</v>
@@ -20376,7 +20310,7 @@
     <row r="389">
       <c r="A389" s="58" t="inlineStr">
         <is>
-          <t>R4-01-C</t>
+          <t>R4-01-D</t>
         </is>
       </c>
       <c r="B389" s="60" t="inlineStr">
@@ -20389,7 +20323,7 @@
       </c>
       <c r="D389" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E389" s="60" t="inlineStr">
@@ -20400,7 +20334,7 @@
       <c r="F389" s="58" t="n"/>
       <c r="G389" s="58" t="n"/>
       <c r="H389" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I389" s="60" t="n">
         <v>21</v>
@@ -20409,7 +20343,7 @@
     <row r="390">
       <c r="A390" s="58" t="inlineStr">
         <is>
-          <t>R4-02-C</t>
+          <t>R4-02-D</t>
         </is>
       </c>
       <c r="B390" s="60" t="inlineStr">
@@ -20422,7 +20356,7 @@
       </c>
       <c r="D390" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E390" s="60" t="inlineStr">
@@ -20433,7 +20367,7 @@
       <c r="F390" s="58" t="n"/>
       <c r="G390" s="58" t="n"/>
       <c r="H390" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I390" s="60" t="n">
         <v>22</v>
@@ -20442,7 +20376,7 @@
     <row r="391">
       <c r="A391" s="58" t="inlineStr">
         <is>
-          <t>R4-03-C</t>
+          <t>R4-03-D</t>
         </is>
       </c>
       <c r="B391" s="60" t="inlineStr">
@@ -20455,7 +20389,7 @@
       </c>
       <c r="D391" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E391" s="60" t="inlineStr">
@@ -20466,7 +20400,7 @@
       <c r="F391" s="58" t="n"/>
       <c r="G391" s="58" t="n"/>
       <c r="H391" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I391" s="60" t="n">
         <v>23</v>
@@ -20475,7 +20409,7 @@
     <row r="392">
       <c r="A392" s="58" t="inlineStr">
         <is>
-          <t>R4-04-C</t>
+          <t>R4-04-D</t>
         </is>
       </c>
       <c r="B392" s="60" t="inlineStr">
@@ -20488,7 +20422,7 @@
       </c>
       <c r="D392" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E392" s="60" t="inlineStr">
@@ -20499,7 +20433,7 @@
       <c r="F392" s="58" t="n"/>
       <c r="G392" s="58" t="n"/>
       <c r="H392" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I392" s="60" t="n">
         <v>24</v>
@@ -20508,7 +20442,7 @@
     <row r="393">
       <c r="A393" s="58" t="inlineStr">
         <is>
-          <t>R4-05-C</t>
+          <t>R4-05-D</t>
         </is>
       </c>
       <c r="B393" s="60" t="inlineStr">
@@ -20521,7 +20455,7 @@
       </c>
       <c r="D393" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E393" s="60" t="inlineStr">
@@ -20532,7 +20466,7 @@
       <c r="F393" s="58" t="n"/>
       <c r="G393" s="58" t="n"/>
       <c r="H393" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I393" s="60" t="n">
         <v>25</v>
@@ -20541,7 +20475,7 @@
     <row r="394">
       <c r="A394" s="58" t="inlineStr">
         <is>
-          <t>R4-06-C</t>
+          <t>R4-06-D</t>
         </is>
       </c>
       <c r="B394" s="60" t="inlineStr">
@@ -20554,7 +20488,7 @@
       </c>
       <c r="D394" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E394" s="60" t="inlineStr">
@@ -20565,7 +20499,7 @@
       <c r="F394" s="58" t="n"/>
       <c r="G394" s="58" t="n"/>
       <c r="H394" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I394" s="60" t="n">
         <v>26</v>
@@ -20574,7 +20508,7 @@
     <row r="395">
       <c r="A395" s="58" t="inlineStr">
         <is>
-          <t>R4-07-C</t>
+          <t>R4-07-D</t>
         </is>
       </c>
       <c r="B395" s="60" t="inlineStr">
@@ -20587,7 +20521,7 @@
       </c>
       <c r="D395" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E395" s="60" t="inlineStr">
@@ -20598,7 +20532,7 @@
       <c r="F395" s="58" t="n"/>
       <c r="G395" s="58" t="n"/>
       <c r="H395" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I395" s="60" t="n">
         <v>27</v>
@@ -20607,7 +20541,7 @@
     <row r="396">
       <c r="A396" s="58" t="inlineStr">
         <is>
-          <t>R4-08-C</t>
+          <t>R4-08-D</t>
         </is>
       </c>
       <c r="B396" s="60" t="inlineStr">
@@ -20620,7 +20554,7 @@
       </c>
       <c r="D396" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E396" s="60" t="inlineStr">
@@ -20631,7 +20565,7 @@
       <c r="F396" s="58" t="n"/>
       <c r="G396" s="58" t="n"/>
       <c r="H396" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I396" s="60" t="n">
         <v>28</v>
@@ -20640,7 +20574,7 @@
     <row r="397">
       <c r="A397" s="58" t="inlineStr">
         <is>
-          <t>R4-09-C</t>
+          <t>R4-09-D</t>
         </is>
       </c>
       <c r="B397" s="60" t="inlineStr">
@@ -20653,7 +20587,7 @@
       </c>
       <c r="D397" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E397" s="60" t="inlineStr">
@@ -20664,7 +20598,7 @@
       <c r="F397" s="58" t="n"/>
       <c r="G397" s="58" t="n"/>
       <c r="H397" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I397" s="60" t="n">
         <v>29</v>
@@ -20673,7 +20607,7 @@
     <row r="398">
       <c r="A398" s="58" t="inlineStr">
         <is>
-          <t>R4-10-C</t>
+          <t>R4-10-D</t>
         </is>
       </c>
       <c r="B398" s="60" t="inlineStr">
@@ -20686,7 +20620,7 @@
       </c>
       <c r="D398" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E398" s="60" t="inlineStr">
@@ -20697,7 +20631,7 @@
       <c r="F398" s="58" t="n"/>
       <c r="G398" s="58" t="n"/>
       <c r="H398" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I398" s="60" t="n">
         <v>30</v>
@@ -20706,7 +20640,7 @@
     <row r="399">
       <c r="A399" s="58" t="inlineStr">
         <is>
-          <t>R4-11-C</t>
+          <t>R4-11-D</t>
         </is>
       </c>
       <c r="B399" s="60" t="inlineStr">
@@ -20719,7 +20653,7 @@
       </c>
       <c r="D399" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E399" s="60" t="inlineStr">
@@ -20730,7 +20664,7 @@
       <c r="F399" s="58" t="n"/>
       <c r="G399" s="58" t="n"/>
       <c r="H399" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I399" s="60" t="n">
         <v>31</v>
@@ -20739,7 +20673,7 @@
     <row r="400">
       <c r="A400" s="58" t="inlineStr">
         <is>
-          <t>R4-12-C</t>
+          <t>R4-12-D</t>
         </is>
       </c>
       <c r="B400" s="60" t="inlineStr">
@@ -20752,7 +20686,7 @@
       </c>
       <c r="D400" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E400" s="60" t="inlineStr">
@@ -20763,7 +20697,7 @@
       <c r="F400" s="58" t="n"/>
       <c r="G400" s="58" t="n"/>
       <c r="H400" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I400" s="60" t="n">
         <v>32</v>
@@ -20772,7 +20706,7 @@
     <row r="401">
       <c r="A401" s="58" t="inlineStr">
         <is>
-          <t>R4-13-C</t>
+          <t>R4-13-D</t>
         </is>
       </c>
       <c r="B401" s="60" t="inlineStr">
@@ -20785,7 +20719,7 @@
       </c>
       <c r="D401" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E401" s="60" t="inlineStr">
@@ -20796,7 +20730,7 @@
       <c r="F401" s="58" t="n"/>
       <c r="G401" s="58" t="n"/>
       <c r="H401" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I401" s="60" t="n">
         <v>33</v>
@@ -20805,7 +20739,7 @@
     <row r="402">
       <c r="A402" s="58" t="inlineStr">
         <is>
-          <t>R4-14-C</t>
+          <t>R4-14-D</t>
         </is>
       </c>
       <c r="B402" s="60" t="inlineStr">
@@ -20818,7 +20752,7 @@
       </c>
       <c r="D402" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E402" s="60" t="inlineStr">
@@ -20829,7 +20763,7 @@
       <c r="F402" s="58" t="n"/>
       <c r="G402" s="58" t="n"/>
       <c r="H402" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I402" s="60" t="n">
         <v>34</v>
@@ -20838,7 +20772,7 @@
     <row r="403">
       <c r="A403" s="58" t="inlineStr">
         <is>
-          <t>R4-15-C</t>
+          <t>R4-15-D</t>
         </is>
       </c>
       <c r="B403" s="60" t="inlineStr">
@@ -20851,7 +20785,7 @@
       </c>
       <c r="D403" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E403" s="60" t="inlineStr">
@@ -20862,7 +20796,7 @@
       <c r="F403" s="58" t="n"/>
       <c r="G403" s="58" t="n"/>
       <c r="H403" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I403" s="60" t="n">
         <v>35</v>
@@ -20871,7 +20805,7 @@
     <row r="404">
       <c r="A404" s="58" t="inlineStr">
         <is>
-          <t>R4-16-C</t>
+          <t>R4-16-D</t>
         </is>
       </c>
       <c r="B404" s="60" t="inlineStr">
@@ -20884,7 +20818,7 @@
       </c>
       <c r="D404" s="60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E404" s="60" t="inlineStr">
@@ -20895,537 +20829,9 @@
       <c r="F404" s="58" t="n"/>
       <c r="G404" s="58" t="n"/>
       <c r="H404" s="60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I404" s="60" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="58" t="inlineStr">
-        <is>
-          <t>R4-01-D</t>
-        </is>
-      </c>
-      <c r="B405" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C405" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D405" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E405" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F405" s="58" t="n"/>
-      <c r="G405" s="58" t="n"/>
-      <c r="H405" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I405" s="60" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" s="58" t="inlineStr">
-        <is>
-          <t>R4-02-D</t>
-        </is>
-      </c>
-      <c r="B406" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C406" s="61" t="n">
-        <v>2</v>
-      </c>
-      <c r="D406" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E406" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F406" s="58" t="n"/>
-      <c r="G406" s="58" t="n"/>
-      <c r="H406" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I406" s="60" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" s="58" t="inlineStr">
-        <is>
-          <t>R4-03-D</t>
-        </is>
-      </c>
-      <c r="B407" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C407" s="61" t="n">
-        <v>3</v>
-      </c>
-      <c r="D407" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E407" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F407" s="58" t="n"/>
-      <c r="G407" s="58" t="n"/>
-      <c r="H407" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I407" s="60" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" s="58" t="inlineStr">
-        <is>
-          <t>R4-04-D</t>
-        </is>
-      </c>
-      <c r="B408" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C408" s="61" t="n">
-        <v>4</v>
-      </c>
-      <c r="D408" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E408" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F408" s="58" t="n"/>
-      <c r="G408" s="58" t="n"/>
-      <c r="H408" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I408" s="60" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" s="58" t="inlineStr">
-        <is>
-          <t>R4-05-D</t>
-        </is>
-      </c>
-      <c r="B409" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C409" s="61" t="n">
-        <v>5</v>
-      </c>
-      <c r="D409" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E409" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F409" s="58" t="n"/>
-      <c r="G409" s="58" t="n"/>
-      <c r="H409" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I409" s="60" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" s="58" t="inlineStr">
-        <is>
-          <t>R4-06-D</t>
-        </is>
-      </c>
-      <c r="B410" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C410" s="61" t="n">
-        <v>6</v>
-      </c>
-      <c r="D410" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E410" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F410" s="58" t="n"/>
-      <c r="G410" s="58" t="n"/>
-      <c r="H410" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I410" s="60" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" s="58" t="inlineStr">
-        <is>
-          <t>R4-07-D</t>
-        </is>
-      </c>
-      <c r="B411" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C411" s="61" t="n">
-        <v>7</v>
-      </c>
-      <c r="D411" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E411" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F411" s="58" t="n"/>
-      <c r="G411" s="58" t="n"/>
-      <c r="H411" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I411" s="60" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" s="58" t="inlineStr">
-        <is>
-          <t>R4-08-D</t>
-        </is>
-      </c>
-      <c r="B412" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C412" s="61" t="n">
-        <v>8</v>
-      </c>
-      <c r="D412" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E412" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F412" s="58" t="n"/>
-      <c r="G412" s="58" t="n"/>
-      <c r="H412" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I412" s="60" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" s="58" t="inlineStr">
-        <is>
-          <t>R4-09-D</t>
-        </is>
-      </c>
-      <c r="B413" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C413" s="61" t="n">
-        <v>9</v>
-      </c>
-      <c r="D413" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E413" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F413" s="58" t="n"/>
-      <c r="G413" s="58" t="n"/>
-      <c r="H413" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I413" s="60" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" s="58" t="inlineStr">
-        <is>
-          <t>R4-10-D</t>
-        </is>
-      </c>
-      <c r="B414" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C414" s="61" t="n">
-        <v>10</v>
-      </c>
-      <c r="D414" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E414" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F414" s="58" t="n"/>
-      <c r="G414" s="58" t="n"/>
-      <c r="H414" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I414" s="60" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" s="58" t="inlineStr">
-        <is>
-          <t>R4-11-D</t>
-        </is>
-      </c>
-      <c r="B415" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C415" s="61" t="n">
-        <v>11</v>
-      </c>
-      <c r="D415" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E415" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F415" s="58" t="n"/>
-      <c r="G415" s="58" t="n"/>
-      <c r="H415" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I415" s="60" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" s="58" t="inlineStr">
-        <is>
-          <t>R4-12-D</t>
-        </is>
-      </c>
-      <c r="B416" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C416" s="61" t="n">
-        <v>12</v>
-      </c>
-      <c r="D416" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E416" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F416" s="58" t="n"/>
-      <c r="G416" s="58" t="n"/>
-      <c r="H416" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I416" s="60" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" s="58" t="inlineStr">
-        <is>
-          <t>R4-13-D</t>
-        </is>
-      </c>
-      <c r="B417" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C417" s="61" t="n">
-        <v>13</v>
-      </c>
-      <c r="D417" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E417" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F417" s="58" t="n"/>
-      <c r="G417" s="58" t="n"/>
-      <c r="H417" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I417" s="60" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" s="58" t="inlineStr">
-        <is>
-          <t>R4-14-D</t>
-        </is>
-      </c>
-      <c r="B418" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C418" s="61" t="n">
-        <v>14</v>
-      </c>
-      <c r="D418" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E418" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F418" s="58" t="n"/>
-      <c r="G418" s="58" t="n"/>
-      <c r="H418" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I418" s="60" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" s="58" t="inlineStr">
-        <is>
-          <t>R4-15-D</t>
-        </is>
-      </c>
-      <c r="B419" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C419" s="61" t="n">
-        <v>15</v>
-      </c>
-      <c r="D419" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E419" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F419" s="58" t="n"/>
-      <c r="G419" s="58" t="n"/>
-      <c r="H419" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I419" s="60" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" s="58" t="inlineStr">
-        <is>
-          <t>R4-16-D</t>
-        </is>
-      </c>
-      <c r="B420" s="60" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="C420" s="61" t="n">
-        <v>16</v>
-      </c>
-      <c r="D420" s="60" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E420" s="60" t="inlineStr">
-        <is>
-          <t>BOX</t>
-        </is>
-      </c>
-      <c r="F420" s="58" t="n"/>
-      <c r="G420" s="58" t="n"/>
-      <c r="H420" s="60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I420" s="60" t="n">
         <v>36</v>
       </c>
     </row>
@@ -21434,16 +20840,16 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F420">
+  <conditionalFormatting sqref="F5:F404">
     <cfRule type="expression" priority="1" dxfId="4">
       <formula>AND($F5&lt;&gt;"",$E5&lt;&gt;"",IFERROR(INDEX(ItemZoneList,MATCH($F5,ItemCodeList,0)),$E5)&lt;&gt;$E5)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="F5:F420" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Item not in this zone" error="That item is not listed for this position's zone (or is not on the Items sheet). Keep it anyway?" type="list" errorStyle="warning">
+    <dataValidation sqref="F5:F404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Item not in this zone" error="That item is not listed for this position's zone (or is not on the Items sheet). Keep it anyway?" type="list" errorStyle="warning">
       <formula1>OFFSET(DDTop,0,IFERROR(MATCH($E5,DDZones,0),0),MAX(1,INDEX(DDCounts,1,IFERROR(MATCH($E5,DDZones,0),0)+1)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G420" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThan">
+    <dataValidation sqref="G5:G404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -22263,7 +21669,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="58" t="n">
         <v>16</v>
